--- a/data/FUSO_Advanced_Model_v2.xlsx
+++ b/data/FUSO_Advanced_Model_v2.xlsx
@@ -16,6 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ECANTER_CAUSAL" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GPC_BRIDGE_STOCK" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOP_TEMPLATE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MONTHLY_DEMAND_DATA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CALC_EXPLAINER" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,14 +26,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="+#,##0;-#,##0;0"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -180,8 +183,86 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00566573"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E8449"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A5276"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00A9CCE3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001A5276"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001E8449"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00E67E22"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="26">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -308,8 +389,73 @@
         <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D1B2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B2E45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A5276"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0392B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E8449"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00148F77"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0ECE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FADBD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F3F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEBD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E67E22"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -433,11 +579,137 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="004A6274"/>
+      </left>
+      <right style="thin">
+        <color rgb="004A6274"/>
+      </right>
+      <top style="thin">
+        <color rgb="004A6274"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="004A6274"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D5D8DC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D5D8DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5D8DC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="001ABC9C"/>
+      </left>
+      <right style="thin">
+        <color rgb="001ABC9C"/>
+      </right>
+      <top style="thin">
+        <color rgb="001ABC9C"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="001ABC9C"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E74C3C"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E74C3C"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E74C3C"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E74C3C"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="001E8449"/>
+      </left>
+      <right style="thin">
+        <color rgb="001E8449"/>
+      </right>
+      <top style="thin">
+        <color rgb="001E8449"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="001E8449"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00148F77"/>
+      </left>
+      <right style="thin">
+        <color rgb="00148F77"/>
+      </right>
+      <top style="thin">
+        <color rgb="00148F77"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00148F77"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BDC3C7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BDC3C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BDC3C7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BDC3C7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E67E22"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E67E22"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E67E22"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E67E22"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="002980B9"/>
+      </left>
+      <right style="thin">
+        <color rgb="002980B9"/>
+      </right>
+      <top style="thin">
+        <color rgb="002980B9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="002980B9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -846,6 +1118,174 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="28" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="30" fillId="33" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="33" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="34" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="31" fillId="34" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="35" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="33" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="31" fillId="36" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="37" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="28" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="32" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="35" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="37" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="34" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="34" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="34" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="37" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="37" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2043,6 +2483,6692 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="155" t="inlineStr">
+        <is>
+          <t>FUSO MEA — Monthly Demand Raw Data (Apr-25 to Mar-26) | Source for All Statistical Calculations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="156" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="B2" s="156" t="inlineStr">
+        <is>
+          <t>Part Description</t>
+        </is>
+      </c>
+      <c r="C2" s="156" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="D2" s="156" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="E2" s="156" t="inlineStr">
+        <is>
+          <t>Unit Cost
+(AED)</t>
+        </is>
+      </c>
+      <c r="F2" s="157" t="inlineStr">
+        <is>
+          <t>Apr-25</t>
+        </is>
+      </c>
+      <c r="G2" s="157" t="inlineStr">
+        <is>
+          <t>May-25</t>
+        </is>
+      </c>
+      <c r="H2" s="157" t="inlineStr">
+        <is>
+          <t>Jun-25</t>
+        </is>
+      </c>
+      <c r="I2" s="157" t="inlineStr">
+        <is>
+          <t>Jul-25</t>
+        </is>
+      </c>
+      <c r="J2" s="157" t="inlineStr">
+        <is>
+          <t>Aug-25</t>
+        </is>
+      </c>
+      <c r="K2" s="157" t="inlineStr">
+        <is>
+          <t>Sep-25</t>
+        </is>
+      </c>
+      <c r="L2" s="157" t="inlineStr">
+        <is>
+          <t>Oct-25</t>
+        </is>
+      </c>
+      <c r="M2" s="157" t="inlineStr">
+        <is>
+          <t>Nov-25</t>
+        </is>
+      </c>
+      <c r="N2" s="157" t="inlineStr">
+        <is>
+          <t>Dec-25</t>
+        </is>
+      </c>
+      <c r="O2" s="157" t="inlineStr">
+        <is>
+          <t>Jan-26</t>
+        </is>
+      </c>
+      <c r="P2" s="157" t="inlineStr">
+        <is>
+          <t>Feb-26</t>
+        </is>
+      </c>
+      <c r="Q2" s="157" t="inlineStr">
+        <is>
+          <t>Mar-26</t>
+        </is>
+      </c>
+      <c r="R2" s="156" t="inlineStr">
+        <is>
+          <t>Annual
+Demand</t>
+        </is>
+      </c>
+      <c r="S2" s="156" t="inlineStr">
+        <is>
+          <t>Mean
+Monthly</t>
+        </is>
+      </c>
+      <c r="T2" s="158" t="inlineStr">
+        <is>
+          <t>Std Dev
+(STDEV formula)</t>
+        </is>
+      </c>
+      <c r="U2" s="158" t="inlineStr">
+        <is>
+          <t>Coeff of
+Variation (CV)</t>
+        </is>
+      </c>
+      <c r="V2" s="159" t="inlineStr">
+        <is>
+          <t>ABC
+Class</t>
+        </is>
+      </c>
+      <c r="W2" s="160" t="inlineStr">
+        <is>
+          <t>XYZ
+Class</t>
+        </is>
+      </c>
+      <c r="X2" s="159" t="inlineStr">
+        <is>
+          <t>Combined
+Class</t>
+        </is>
+      </c>
+      <c r="Y2" s="156" t="inlineStr">
+        <is>
+          <t>Annual
+Value (AED)</t>
+        </is>
+      </c>
+      <c r="Z2" s="156" t="inlineStr">
+        <is>
+          <t>Cumul
+Value %</t>
+        </is>
+      </c>
+      <c r="AA2" s="159" t="inlineStr">
+        <is>
+          <t>ABC
+Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-CLT-006</t>
+        </is>
+      </c>
+      <c r="B3" s="162" t="inlineStr">
+        <is>
+          <t>Clutch Disc Assy</t>
+        </is>
+      </c>
+      <c r="C3" s="163" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D3" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E3" s="164" t="n">
+        <v>420</v>
+      </c>
+      <c r="F3" s="165" t="n">
+        <v>49</v>
+      </c>
+      <c r="G3" s="165" t="n">
+        <v>62</v>
+      </c>
+      <c r="H3" s="165" t="n">
+        <v>44</v>
+      </c>
+      <c r="I3" s="165" t="n">
+        <v>36</v>
+      </c>
+      <c r="J3" s="165" t="n">
+        <v>52</v>
+      </c>
+      <c r="K3" s="165" t="n">
+        <v>55</v>
+      </c>
+      <c r="L3" s="165" t="n">
+        <v>53</v>
+      </c>
+      <c r="M3" s="165" t="n">
+        <v>55</v>
+      </c>
+      <c r="N3" s="165" t="n">
+        <v>50</v>
+      </c>
+      <c r="O3" s="165" t="n">
+        <v>46</v>
+      </c>
+      <c r="P3" s="165" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q3" s="165" t="n">
+        <v>49</v>
+      </c>
+      <c r="R3" s="166">
+        <f>SUM(F3:Q3)</f>
+        <v/>
+      </c>
+      <c r="S3" s="167">
+        <f>R3/12</f>
+        <v/>
+      </c>
+      <c r="T3" s="168">
+        <f>STDEV(F3:Q3)</f>
+        <v/>
+      </c>
+      <c r="U3" s="169">
+        <f>IF(S3=0,9999,T3/S3)</f>
+        <v/>
+      </c>
+      <c r="V3" s="170">
+        <f>IF(Z3&lt;=0.7,"A",IF(Z3&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W3" s="171">
+        <f>IF(U3&lt;0.1,"X",IF(U3&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X3" s="172">
+        <f>V3&amp;W3</f>
+        <v/>
+      </c>
+      <c r="Y3" s="173">
+        <f>E3*R3</f>
+        <v/>
+      </c>
+      <c r="Z3" s="174">
+        <f>Y3/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA3" s="175">
+        <f>IF(V3="A","✓ A-CLASS",IF(V3="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-SHK-012</t>
+        </is>
+      </c>
+      <c r="B4" s="177" t="inlineStr">
+        <is>
+          <t>Shock Absorber Front</t>
+        </is>
+      </c>
+      <c r="C4" s="178" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D4" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E4" s="179" t="n">
+        <v>680</v>
+      </c>
+      <c r="F4" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="165" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="165" t="n">
+        <v>47</v>
+      </c>
+      <c r="K4" s="165" t="n">
+        <v>60</v>
+      </c>
+      <c r="L4" s="165" t="n">
+        <v>54</v>
+      </c>
+      <c r="M4" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="165" t="n">
+        <v>99</v>
+      </c>
+      <c r="P4" s="165" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q4" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="166">
+        <f>SUM(F4:Q4)</f>
+        <v/>
+      </c>
+      <c r="S4" s="167">
+        <f>R4/12</f>
+        <v/>
+      </c>
+      <c r="T4" s="168">
+        <f>STDEV(F4:Q4)</f>
+        <v/>
+      </c>
+      <c r="U4" s="169">
+        <f>IF(S4=0,9999,T4/S4)</f>
+        <v/>
+      </c>
+      <c r="V4" s="170">
+        <f>IF(Z4&lt;=0.7,"A",IF(Z4&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W4" s="171">
+        <f>IF(U4&lt;0.1,"X",IF(U4&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X4" s="172">
+        <f>V4&amp;W4</f>
+        <v/>
+      </c>
+      <c r="Y4" s="173">
+        <f>E4*R4</f>
+        <v/>
+      </c>
+      <c r="Z4" s="174">
+        <f>Y4/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA4" s="175">
+        <f>IF(V4="A","✓ A-CLASS",IF(V4="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-ALT-011</t>
+        </is>
+      </c>
+      <c r="B5" s="162" t="inlineStr">
+        <is>
+          <t>Alternator 24V</t>
+        </is>
+      </c>
+      <c r="C5" s="163" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D5" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E5" s="164" t="n">
+        <v>950</v>
+      </c>
+      <c r="F5" s="165" t="n">
+        <v>44</v>
+      </c>
+      <c r="G5" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="165" t="n">
+        <v>65</v>
+      </c>
+      <c r="I5" s="165" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="165" t="n">
+        <v>27</v>
+      </c>
+      <c r="L5" s="165" t="n">
+        <v>26</v>
+      </c>
+      <c r="M5" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="165" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q5" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="166">
+        <f>SUM(F5:Q5)</f>
+        <v/>
+      </c>
+      <c r="S5" s="167">
+        <f>R5/12</f>
+        <v/>
+      </c>
+      <c r="T5" s="168">
+        <f>STDEV(F5:Q5)</f>
+        <v/>
+      </c>
+      <c r="U5" s="169">
+        <f>IF(S5=0,9999,T5/S5)</f>
+        <v/>
+      </c>
+      <c r="V5" s="170">
+        <f>IF(Z5&lt;=0.7,"A",IF(Z5&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W5" s="171">
+        <f>IF(U5&lt;0.1,"X",IF(U5&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X5" s="172">
+        <f>V5&amp;W5</f>
+        <v/>
+      </c>
+      <c r="Y5" s="173">
+        <f>E5*R5</f>
+        <v/>
+      </c>
+      <c r="Z5" s="174">
+        <f>Y5/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA5" s="175">
+        <f>IF(V5="A","✓ A-CLASS",IF(V5="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-INJ-013</t>
+        </is>
+      </c>
+      <c r="B6" s="177" t="inlineStr">
+        <is>
+          <t>Injector Nozzle</t>
+        </is>
+      </c>
+      <c r="C6" s="178" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D6" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E6" s="179" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F6" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="165" t="n">
+        <v>34</v>
+      </c>
+      <c r="I6" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="165" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" s="165" t="n">
+        <v>49</v>
+      </c>
+      <c r="L6" s="165" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="165" t="n">
+        <v>28</v>
+      </c>
+      <c r="P6" s="165" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q6" s="165" t="n">
+        <v>26</v>
+      </c>
+      <c r="R6" s="166">
+        <f>SUM(F6:Q6)</f>
+        <v/>
+      </c>
+      <c r="S6" s="167">
+        <f>R6/12</f>
+        <v/>
+      </c>
+      <c r="T6" s="168">
+        <f>STDEV(F6:Q6)</f>
+        <v/>
+      </c>
+      <c r="U6" s="169">
+        <f>IF(S6=0,9999,T6/S6)</f>
+        <v/>
+      </c>
+      <c r="V6" s="170">
+        <f>IF(Z6&lt;=0.7,"A",IF(Z6&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W6" s="171">
+        <f>IF(U6&lt;0.1,"X",IF(U6&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X6" s="172">
+        <f>V6&amp;W6</f>
+        <v/>
+      </c>
+      <c r="Y6" s="173">
+        <f>E6*R6</f>
+        <v/>
+      </c>
+      <c r="Z6" s="174">
+        <f>Y6/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA6" s="175">
+        <f>IF(V6="A","✓ A-CLASS",IF(V6="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-STR-016</t>
+        </is>
+      </c>
+      <c r="B7" s="162" t="inlineStr">
+        <is>
+          <t>Steering Pump</t>
+        </is>
+      </c>
+      <c r="C7" s="163" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D7" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E7" s="164" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F7" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="165" t="n">
+        <v>166</v>
+      </c>
+      <c r="I7" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="165" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="166">
+        <f>SUM(F7:Q7)</f>
+        <v/>
+      </c>
+      <c r="S7" s="167">
+        <f>R7/12</f>
+        <v/>
+      </c>
+      <c r="T7" s="168">
+        <f>STDEV(F7:Q7)</f>
+        <v/>
+      </c>
+      <c r="U7" s="169">
+        <f>IF(S7=0,9999,T7/S7)</f>
+        <v/>
+      </c>
+      <c r="V7" s="170">
+        <f>IF(Z7&lt;=0.7,"A",IF(Z7&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W7" s="171">
+        <f>IF(U7&lt;0.1,"X",IF(U7&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X7" s="172">
+        <f>V7&amp;W7</f>
+        <v/>
+      </c>
+      <c r="Y7" s="173">
+        <f>E7*R7</f>
+        <v/>
+      </c>
+      <c r="Z7" s="174">
+        <f>Y7/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA7" s="175">
+        <f>IF(V7="A","✓ A-CLASS",IF(V7="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-WPM-007</t>
+        </is>
+      </c>
+      <c r="B8" s="177" t="inlineStr">
+        <is>
+          <t>Water Pump Assy</t>
+        </is>
+      </c>
+      <c r="C8" s="178" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D8" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E8" s="179" t="n">
+        <v>380</v>
+      </c>
+      <c r="F8" s="165" t="n">
+        <v>50</v>
+      </c>
+      <c r="G8" s="165" t="n">
+        <v>44</v>
+      </c>
+      <c r="H8" s="165" t="n">
+        <v>49</v>
+      </c>
+      <c r="I8" s="165" t="n">
+        <v>47</v>
+      </c>
+      <c r="J8" s="165" t="n">
+        <v>38</v>
+      </c>
+      <c r="K8" s="165" t="n">
+        <v>40</v>
+      </c>
+      <c r="L8" s="165" t="n">
+        <v>38</v>
+      </c>
+      <c r="M8" s="165" t="n">
+        <v>47</v>
+      </c>
+      <c r="N8" s="165" t="n">
+        <v>51</v>
+      </c>
+      <c r="O8" s="165" t="n">
+        <v>33</v>
+      </c>
+      <c r="P8" s="165" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q8" s="165" t="n">
+        <v>42</v>
+      </c>
+      <c r="R8" s="166">
+        <f>SUM(F8:Q8)</f>
+        <v/>
+      </c>
+      <c r="S8" s="167">
+        <f>R8/12</f>
+        <v/>
+      </c>
+      <c r="T8" s="168">
+        <f>STDEV(F8:Q8)</f>
+        <v/>
+      </c>
+      <c r="U8" s="169">
+        <f>IF(S8=0,9999,T8/S8)</f>
+        <v/>
+      </c>
+      <c r="V8" s="170">
+        <f>IF(Z8&lt;=0.7,"A",IF(Z8&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W8" s="171">
+        <f>IF(U8&lt;0.1,"X",IF(U8&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X8" s="172">
+        <f>V8&amp;W8</f>
+        <v/>
+      </c>
+      <c r="Y8" s="173">
+        <f>E8*R8</f>
+        <v/>
+      </c>
+      <c r="Z8" s="174">
+        <f>Y8/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA8" s="175">
+        <f>IF(V8="A","✓ A-CLASS",IF(V8="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-TRB-021</t>
+        </is>
+      </c>
+      <c r="B9" s="162" t="inlineStr">
+        <is>
+          <t>Turbocharger Assy</t>
+        </is>
+      </c>
+      <c r="C9" s="163" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D9" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E9" s="164" t="n">
+        <v>3800</v>
+      </c>
+      <c r="F9" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="165" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="165" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" s="165" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="165" t="n">
+        <v>11</v>
+      </c>
+      <c r="L9" s="165" t="n">
+        <v>18</v>
+      </c>
+      <c r="M9" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="165" t="n">
+        <v>9</v>
+      </c>
+      <c r="R9" s="166">
+        <f>SUM(F9:Q9)</f>
+        <v/>
+      </c>
+      <c r="S9" s="167">
+        <f>R9/12</f>
+        <v/>
+      </c>
+      <c r="T9" s="168">
+        <f>STDEV(F9:Q9)</f>
+        <v/>
+      </c>
+      <c r="U9" s="169">
+        <f>IF(S9=0,9999,T9/S9)</f>
+        <v/>
+      </c>
+      <c r="V9" s="170">
+        <f>IF(Z9&lt;=0.7,"A",IF(Z9&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W9" s="171">
+        <f>IF(U9&lt;0.1,"X",IF(U9&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X9" s="172">
+        <f>V9&amp;W9</f>
+        <v/>
+      </c>
+      <c r="Y9" s="173">
+        <f>E9*R9</f>
+        <v/>
+      </c>
+      <c r="Z9" s="174">
+        <f>Y9/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA9" s="175">
+        <f>IF(V9="A","✓ A-CLASS",IF(V9="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-FUL-017</t>
+        </is>
+      </c>
+      <c r="B10" s="177" t="inlineStr">
+        <is>
+          <t>Fuel Pump Assy</t>
+        </is>
+      </c>
+      <c r="C10" s="178" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D10" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E10" s="179" t="n">
+        <v>780</v>
+      </c>
+      <c r="F10" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="165" t="n">
+        <v>59</v>
+      </c>
+      <c r="H10" s="165" t="n">
+        <v>37</v>
+      </c>
+      <c r="I10" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="165" t="n">
+        <v>132</v>
+      </c>
+      <c r="P10" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="166">
+        <f>SUM(F10:Q10)</f>
+        <v/>
+      </c>
+      <c r="S10" s="167">
+        <f>R10/12</f>
+        <v/>
+      </c>
+      <c r="T10" s="168">
+        <f>STDEV(F10:Q10)</f>
+        <v/>
+      </c>
+      <c r="U10" s="169">
+        <f>IF(S10=0,9999,T10/S10)</f>
+        <v/>
+      </c>
+      <c r="V10" s="170">
+        <f>IF(Z10&lt;=0.7,"A",IF(Z10&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W10" s="171">
+        <f>IF(U10&lt;0.1,"X",IF(U10&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X10" s="172">
+        <f>V10&amp;W10</f>
+        <v/>
+      </c>
+      <c r="Y10" s="173">
+        <f>E10*R10</f>
+        <v/>
+      </c>
+      <c r="Z10" s="174">
+        <f>Y10/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA10" s="175">
+        <f>IF(V10="A","✓ A-CLASS",IF(V10="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-EXH-015</t>
+        </is>
+      </c>
+      <c r="B11" s="162" t="inlineStr">
+        <is>
+          <t>Exhaust Manifold</t>
+        </is>
+      </c>
+      <c r="C11" s="163" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D11" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E11" s="164" t="n">
+        <v>840</v>
+      </c>
+      <c r="F11" s="165" t="n">
+        <v>53</v>
+      </c>
+      <c r="G11" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="165" t="n">
+        <v>39</v>
+      </c>
+      <c r="I11" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="165" t="n">
+        <v>60</v>
+      </c>
+      <c r="M11" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="166">
+        <f>SUM(F11:Q11)</f>
+        <v/>
+      </c>
+      <c r="S11" s="167">
+        <f>R11/12</f>
+        <v/>
+      </c>
+      <c r="T11" s="168">
+        <f>STDEV(F11:Q11)</f>
+        <v/>
+      </c>
+      <c r="U11" s="169">
+        <f>IF(S11=0,9999,T11/S11)</f>
+        <v/>
+      </c>
+      <c r="V11" s="170">
+        <f>IF(Z11&lt;=0.7,"A",IF(Z11&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W11" s="171">
+        <f>IF(U11&lt;0.1,"X",IF(U11&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X11" s="172">
+        <f>V11&amp;W11</f>
+        <v/>
+      </c>
+      <c r="Y11" s="173">
+        <f>E11*R11</f>
+        <v/>
+      </c>
+      <c r="Z11" s="174">
+        <f>Y11/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA11" s="175">
+        <f>IF(V11="A","✓ A-CLASS",IF(V11="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-TRN-014</t>
+        </is>
+      </c>
+      <c r="B12" s="177" t="inlineStr">
+        <is>
+          <t>Transmission Mount</t>
+        </is>
+      </c>
+      <c r="C12" s="178" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D12" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E12" s="179" t="n">
+        <v>560</v>
+      </c>
+      <c r="F12" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="165" t="n">
+        <v>71</v>
+      </c>
+      <c r="J12" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="165" t="n">
+        <v>24</v>
+      </c>
+      <c r="M12" s="165" t="n">
+        <v>83</v>
+      </c>
+      <c r="N12" s="165" t="n">
+        <v>44</v>
+      </c>
+      <c r="O12" s="165" t="n">
+        <v>81</v>
+      </c>
+      <c r="P12" s="165" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q12" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="166">
+        <f>SUM(F12:Q12)</f>
+        <v/>
+      </c>
+      <c r="S12" s="167">
+        <f>R12/12</f>
+        <v/>
+      </c>
+      <c r="T12" s="168">
+        <f>STDEV(F12:Q12)</f>
+        <v/>
+      </c>
+      <c r="U12" s="169">
+        <f>IF(S12=0,9999,T12/S12)</f>
+        <v/>
+      </c>
+      <c r="V12" s="170">
+        <f>IF(Z12&lt;=0.7,"A",IF(Z12&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W12" s="171">
+        <f>IF(U12&lt;0.1,"X",IF(U12&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X12" s="172">
+        <f>V12&amp;W12</f>
+        <v/>
+      </c>
+      <c r="Y12" s="173">
+        <f>E12*R12</f>
+        <v/>
+      </c>
+      <c r="Z12" s="174">
+        <f>Y12/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA12" s="175">
+        <f>IF(V12="A","✓ A-CLASS",IF(V12="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-BRG-005</t>
+        </is>
+      </c>
+      <c r="B13" s="162" t="inlineStr">
+        <is>
+          <t>Wheel Bearing Front</t>
+        </is>
+      </c>
+      <c r="C13" s="163" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D13" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E13" s="164" t="n">
+        <v>180</v>
+      </c>
+      <c r="F13" s="165" t="n">
+        <v>59</v>
+      </c>
+      <c r="G13" s="165" t="n">
+        <v>69</v>
+      </c>
+      <c r="H13" s="165" t="n">
+        <v>76</v>
+      </c>
+      <c r="I13" s="165" t="n">
+        <v>78</v>
+      </c>
+      <c r="J13" s="165" t="n">
+        <v>77</v>
+      </c>
+      <c r="K13" s="165" t="n">
+        <v>35</v>
+      </c>
+      <c r="L13" s="165" t="n">
+        <v>68</v>
+      </c>
+      <c r="M13" s="165" t="n">
+        <v>76</v>
+      </c>
+      <c r="N13" s="165" t="n">
+        <v>76</v>
+      </c>
+      <c r="O13" s="165" t="n">
+        <v>57</v>
+      </c>
+      <c r="P13" s="165" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q13" s="165" t="n">
+        <v>69</v>
+      </c>
+      <c r="R13" s="166">
+        <f>SUM(F13:Q13)</f>
+        <v/>
+      </c>
+      <c r="S13" s="167">
+        <f>R13/12</f>
+        <v/>
+      </c>
+      <c r="T13" s="168">
+        <f>STDEV(F13:Q13)</f>
+        <v/>
+      </c>
+      <c r="U13" s="169">
+        <f>IF(S13=0,9999,T13/S13)</f>
+        <v/>
+      </c>
+      <c r="V13" s="170">
+        <f>IF(Z13&lt;=0.7,"A",IF(Z13&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W13" s="171">
+        <f>IF(U13&lt;0.1,"X",IF(U13&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X13" s="172">
+        <f>V13&amp;W13</f>
+        <v/>
+      </c>
+      <c r="Y13" s="173">
+        <f>E13*R13</f>
+        <v/>
+      </c>
+      <c r="Z13" s="174">
+        <f>Y13/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA13" s="175">
+        <f>IF(V13="A","✓ A-CLASS",IF(V13="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-DIF-018</t>
+        </is>
+      </c>
+      <c r="B14" s="177" t="inlineStr">
+        <is>
+          <t>Differential Fluid Kit</t>
+        </is>
+      </c>
+      <c r="C14" s="178" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D14" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E14" s="179" t="n">
+        <v>290</v>
+      </c>
+      <c r="F14" s="165" t="n">
+        <v>59</v>
+      </c>
+      <c r="G14" s="165" t="n">
+        <v>44</v>
+      </c>
+      <c r="H14" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="165" t="n">
+        <v>31</v>
+      </c>
+      <c r="K14" s="165" t="n">
+        <v>105</v>
+      </c>
+      <c r="L14" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="165" t="n">
+        <v>49</v>
+      </c>
+      <c r="N14" s="165" t="n">
+        <v>70</v>
+      </c>
+      <c r="O14" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="165" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q14" s="165" t="n">
+        <v>62</v>
+      </c>
+      <c r="R14" s="166">
+        <f>SUM(F14:Q14)</f>
+        <v/>
+      </c>
+      <c r="S14" s="167">
+        <f>R14/12</f>
+        <v/>
+      </c>
+      <c r="T14" s="168">
+        <f>STDEV(F14:Q14)</f>
+        <v/>
+      </c>
+      <c r="U14" s="169">
+        <f>IF(S14=0,9999,T14/S14)</f>
+        <v/>
+      </c>
+      <c r="V14" s="170">
+        <f>IF(Z14&lt;=0.7,"A",IF(Z14&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W14" s="171">
+        <f>IF(U14&lt;0.1,"X",IF(U14&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X14" s="172">
+        <f>V14&amp;W14</f>
+        <v/>
+      </c>
+      <c r="Y14" s="173">
+        <f>E14*R14</f>
+        <v/>
+      </c>
+      <c r="Z14" s="174">
+        <f>Y14/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA14" s="175">
+        <f>IF(V14="A","✓ A-CLASS",IF(V14="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-CLR-020</t>
+        </is>
+      </c>
+      <c r="B15" s="162" t="inlineStr">
+        <is>
+          <t>Coolant (20L drum)</t>
+        </is>
+      </c>
+      <c r="C15" s="163" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D15" s="163" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E15" s="164" t="n">
+        <v>220</v>
+      </c>
+      <c r="F15" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="165" t="n">
+        <v>248</v>
+      </c>
+      <c r="M15" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="165" t="n">
+        <v>292</v>
+      </c>
+      <c r="O15" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="166">
+        <f>SUM(F15:Q15)</f>
+        <v/>
+      </c>
+      <c r="S15" s="167">
+        <f>R15/12</f>
+        <v/>
+      </c>
+      <c r="T15" s="168">
+        <f>STDEV(F15:Q15)</f>
+        <v/>
+      </c>
+      <c r="U15" s="169">
+        <f>IF(S15=0,9999,T15/S15)</f>
+        <v/>
+      </c>
+      <c r="V15" s="170">
+        <f>IF(Z15&lt;=0.7,"A",IF(Z15&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W15" s="171">
+        <f>IF(U15&lt;0.1,"X",IF(U15&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X15" s="172">
+        <f>V15&amp;W15</f>
+        <v/>
+      </c>
+      <c r="Y15" s="173">
+        <f>E15*R15</f>
+        <v/>
+      </c>
+      <c r="Z15" s="174">
+        <f>Y15/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA15" s="175">
+        <f>IF(V15="A","✓ A-CLASS",IF(V15="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-BLT-004</t>
+        </is>
+      </c>
+      <c r="B16" s="177" t="inlineStr">
+        <is>
+          <t>Drive Belt Set</t>
+        </is>
+      </c>
+      <c r="C16" s="178" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D16" s="178" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E16" s="179" t="n">
+        <v>120</v>
+      </c>
+      <c r="F16" s="165" t="n">
+        <v>69</v>
+      </c>
+      <c r="G16" s="165" t="n">
+        <v>69</v>
+      </c>
+      <c r="H16" s="165" t="n">
+        <v>66</v>
+      </c>
+      <c r="I16" s="165" t="n">
+        <v>64</v>
+      </c>
+      <c r="J16" s="165" t="n">
+        <v>108</v>
+      </c>
+      <c r="K16" s="165" t="n">
+        <v>83</v>
+      </c>
+      <c r="L16" s="165" t="n">
+        <v>75</v>
+      </c>
+      <c r="M16" s="165" t="n">
+        <v>74</v>
+      </c>
+      <c r="N16" s="165" t="n">
+        <v>78</v>
+      </c>
+      <c r="O16" s="165" t="n">
+        <v>90</v>
+      </c>
+      <c r="P16" s="165" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q16" s="165" t="n">
+        <v>75</v>
+      </c>
+      <c r="R16" s="166">
+        <f>SUM(F16:Q16)</f>
+        <v/>
+      </c>
+      <c r="S16" s="167">
+        <f>R16/12</f>
+        <v/>
+      </c>
+      <c r="T16" s="168">
+        <f>STDEV(F16:Q16)</f>
+        <v/>
+      </c>
+      <c r="U16" s="169">
+        <f>IF(S16=0,9999,T16/S16)</f>
+        <v/>
+      </c>
+      <c r="V16" s="170">
+        <f>IF(Z16&lt;=0.7,"A",IF(Z16&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W16" s="171">
+        <f>IF(U16&lt;0.1,"X",IF(U16&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X16" s="172">
+        <f>V16&amp;W16</f>
+        <v/>
+      </c>
+      <c r="Y16" s="173">
+        <f>E16*R16</f>
+        <v/>
+      </c>
+      <c r="Z16" s="174">
+        <f>Y16/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA16" s="175">
+        <f>IF(V16="A","✓ A-CLASS",IF(V16="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-EGR-040</t>
+        </is>
+      </c>
+      <c r="B17" s="162" t="inlineStr">
+        <is>
+          <t>EGR Valve</t>
+        </is>
+      </c>
+      <c r="C17" s="163" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D17" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E17" s="164" t="n">
+        <v>960</v>
+      </c>
+      <c r="F17" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="165" t="n">
+        <v>11</v>
+      </c>
+      <c r="L17" s="165" t="n">
+        <v>25</v>
+      </c>
+      <c r="M17" s="165" t="n">
+        <v>67</v>
+      </c>
+      <c r="N17" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="165" t="n">
+        <v>20</v>
+      </c>
+      <c r="P17" s="165" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q17" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="166">
+        <f>SUM(F17:Q17)</f>
+        <v/>
+      </c>
+      <c r="S17" s="167">
+        <f>R17/12</f>
+        <v/>
+      </c>
+      <c r="T17" s="168">
+        <f>STDEV(F17:Q17)</f>
+        <v/>
+      </c>
+      <c r="U17" s="169">
+        <f>IF(S17=0,9999,T17/S17)</f>
+        <v/>
+      </c>
+      <c r="V17" s="170">
+        <f>IF(Z17&lt;=0.7,"A",IF(Z17&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W17" s="171">
+        <f>IF(U17&lt;0.1,"X",IF(U17&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X17" s="172">
+        <f>V17&amp;W17</f>
+        <v/>
+      </c>
+      <c r="Y17" s="173">
+        <f>E17*R17</f>
+        <v/>
+      </c>
+      <c r="Z17" s="174">
+        <f>Y17/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA17" s="175">
+        <f>IF(V17="A","✓ A-CLASS",IF(V17="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-SBU-050</t>
+        </is>
+      </c>
+      <c r="B18" s="177" t="inlineStr">
+        <is>
+          <t>Starter Motor</t>
+        </is>
+      </c>
+      <c r="C18" s="178" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D18" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E18" s="179" t="n">
+        <v>620</v>
+      </c>
+      <c r="F18" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="165" t="n">
+        <v>23</v>
+      </c>
+      <c r="I18" s="165" t="n">
+        <v>29</v>
+      </c>
+      <c r="J18" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="165" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="165" t="n">
+        <v>35</v>
+      </c>
+      <c r="N18" s="165" t="n">
+        <v>31</v>
+      </c>
+      <c r="O18" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="165" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q18" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="166">
+        <f>SUM(F18:Q18)</f>
+        <v/>
+      </c>
+      <c r="S18" s="167">
+        <f>R18/12</f>
+        <v/>
+      </c>
+      <c r="T18" s="168">
+        <f>STDEV(F18:Q18)</f>
+        <v/>
+      </c>
+      <c r="U18" s="169">
+        <f>IF(S18=0,9999,T18/S18)</f>
+        <v/>
+      </c>
+      <c r="V18" s="170">
+        <f>IF(Z18&lt;=0.7,"A",IF(Z18&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W18" s="171">
+        <f>IF(U18&lt;0.1,"X",IF(U18&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X18" s="172">
+        <f>V18&amp;W18</f>
+        <v/>
+      </c>
+      <c r="Y18" s="173">
+        <f>E18*R18</f>
+        <v/>
+      </c>
+      <c r="Z18" s="174">
+        <f>Y18/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA18" s="175">
+        <f>IF(V18="A","✓ A-CLASS",IF(V18="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-BAT-032</t>
+        </is>
+      </c>
+      <c r="B19" s="162" t="inlineStr">
+        <is>
+          <t>Battery Cell Module</t>
+        </is>
+      </c>
+      <c r="C19" s="163" t="inlineStr">
+        <is>
+          <t>eCanter</t>
+        </is>
+      </c>
+      <c r="D19" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E19" s="164" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F19" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="165" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="166">
+        <f>SUM(F19:Q19)</f>
+        <v/>
+      </c>
+      <c r="S19" s="167">
+        <f>R19/12</f>
+        <v/>
+      </c>
+      <c r="T19" s="168">
+        <f>STDEV(F19:Q19)</f>
+        <v/>
+      </c>
+      <c r="U19" s="169">
+        <f>IF(S19=0,9999,T19/S19)</f>
+        <v/>
+      </c>
+      <c r="V19" s="170">
+        <f>IF(Z19&lt;=0.7,"A",IF(Z19&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W19" s="171">
+        <f>IF(U19&lt;0.1,"X",IF(U19&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X19" s="172">
+        <f>V19&amp;W19</f>
+        <v/>
+      </c>
+      <c r="Y19" s="173">
+        <f>E19*R19</f>
+        <v/>
+      </c>
+      <c r="Z19" s="174">
+        <f>Y19/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA19" s="175">
+        <f>IF(V19="A","✓ A-CLASS",IF(V19="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-SPR-049</t>
+        </is>
+      </c>
+      <c r="B20" s="177" t="inlineStr">
+        <is>
+          <t>Leaf Spring (pair)</t>
+        </is>
+      </c>
+      <c r="C20" s="178" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D20" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E20" s="179" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F20" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="165" t="n">
+        <v>60</v>
+      </c>
+      <c r="K20" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="166">
+        <f>SUM(F20:Q20)</f>
+        <v/>
+      </c>
+      <c r="S20" s="167">
+        <f>R20/12</f>
+        <v/>
+      </c>
+      <c r="T20" s="168">
+        <f>STDEV(F20:Q20)</f>
+        <v/>
+      </c>
+      <c r="U20" s="169">
+        <f>IF(S20=0,9999,T20/S20)</f>
+        <v/>
+      </c>
+      <c r="V20" s="170">
+        <f>IF(Z20&lt;=0.7,"A",IF(Z20&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W20" s="171">
+        <f>IF(U20&lt;0.1,"X",IF(U20&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X20" s="172">
+        <f>V20&amp;W20</f>
+        <v/>
+      </c>
+      <c r="Y20" s="173">
+        <f>E20*R20</f>
+        <v/>
+      </c>
+      <c r="Z20" s="174">
+        <f>Y20/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA20" s="175">
+        <f>IF(V20="A","✓ A-CLASS",IF(V20="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-BRK-001</t>
+        </is>
+      </c>
+      <c r="B21" s="162" t="inlineStr">
+        <is>
+          <t>Brake Pad Set Front</t>
+        </is>
+      </c>
+      <c r="C21" s="163" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D21" s="163" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E21" s="164" t="n">
+        <v>85</v>
+      </c>
+      <c r="F21" s="165" t="n">
+        <v>114</v>
+      </c>
+      <c r="G21" s="165" t="n">
+        <v>92</v>
+      </c>
+      <c r="H21" s="165" t="n">
+        <v>119</v>
+      </c>
+      <c r="I21" s="165" t="n">
+        <v>90</v>
+      </c>
+      <c r="J21" s="165" t="n">
+        <v>105</v>
+      </c>
+      <c r="K21" s="165" t="n">
+        <v>103</v>
+      </c>
+      <c r="L21" s="165" t="n">
+        <v>90</v>
+      </c>
+      <c r="M21" s="165" t="n">
+        <v>111</v>
+      </c>
+      <c r="N21" s="165" t="n">
+        <v>81</v>
+      </c>
+      <c r="O21" s="165" t="n">
+        <v>111</v>
+      </c>
+      <c r="P21" s="165" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q21" s="165" t="n">
+        <v>86</v>
+      </c>
+      <c r="R21" s="166">
+        <f>SUM(F21:Q21)</f>
+        <v/>
+      </c>
+      <c r="S21" s="167">
+        <f>R21/12</f>
+        <v/>
+      </c>
+      <c r="T21" s="168">
+        <f>STDEV(F21:Q21)</f>
+        <v/>
+      </c>
+      <c r="U21" s="169">
+        <f>IF(S21=0,9999,T21/S21)</f>
+        <v/>
+      </c>
+      <c r="V21" s="170">
+        <f>IF(Z21&lt;=0.7,"A",IF(Z21&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W21" s="171">
+        <f>IF(U21&lt;0.1,"X",IF(U21&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X21" s="172">
+        <f>V21&amp;W21</f>
+        <v/>
+      </c>
+      <c r="Y21" s="173">
+        <f>E21*R21</f>
+        <v/>
+      </c>
+      <c r="Z21" s="174">
+        <f>Y21/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="175">
+        <f>IF(V21="A","✓ A-CLASS",IF(V21="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-ECU-031</t>
+        </is>
+      </c>
+      <c r="B22" s="177" t="inlineStr">
+        <is>
+          <t>eCanter ECU Module</t>
+        </is>
+      </c>
+      <c r="C22" s="178" t="inlineStr">
+        <is>
+          <t>eCanter</t>
+        </is>
+      </c>
+      <c r="D22" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E22" s="179" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F22" s="165" t="n">
+        <v>12</v>
+      </c>
+      <c r="G22" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="166">
+        <f>SUM(F22:Q22)</f>
+        <v/>
+      </c>
+      <c r="S22" s="167">
+        <f>R22/12</f>
+        <v/>
+      </c>
+      <c r="T22" s="168">
+        <f>STDEV(F22:Q22)</f>
+        <v/>
+      </c>
+      <c r="U22" s="169">
+        <f>IF(S22=0,9999,T22/S22)</f>
+        <v/>
+      </c>
+      <c r="V22" s="170">
+        <f>IF(Z22&lt;=0.7,"A",IF(Z22&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W22" s="171">
+        <f>IF(U22&lt;0.1,"X",IF(U22&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X22" s="172">
+        <f>V22&amp;W22</f>
+        <v/>
+      </c>
+      <c r="Y22" s="173">
+        <f>E22*R22</f>
+        <v/>
+      </c>
+      <c r="Z22" s="174">
+        <f>Y22/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA22" s="175">
+        <f>IF(V22="A","✓ A-CLASS",IF(V22="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-HUB-045</t>
+        </is>
+      </c>
+      <c r="B23" s="162" t="inlineStr">
+        <is>
+          <t>Wheel Hub Assy</t>
+        </is>
+      </c>
+      <c r="C23" s="163" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D23" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E23" s="164" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F23" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="165" t="n">
+        <v>42</v>
+      </c>
+      <c r="H23" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="165" t="n">
+        <v>40</v>
+      </c>
+      <c r="L23" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="165" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q23" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="166">
+        <f>SUM(F23:Q23)</f>
+        <v/>
+      </c>
+      <c r="S23" s="167">
+        <f>R23/12</f>
+        <v/>
+      </c>
+      <c r="T23" s="168">
+        <f>STDEV(F23:Q23)</f>
+        <v/>
+      </c>
+      <c r="U23" s="169">
+        <f>IF(S23=0,9999,T23/S23)</f>
+        <v/>
+      </c>
+      <c r="V23" s="170">
+        <f>IF(Z23&lt;=0.7,"A",IF(Z23&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W23" s="171">
+        <f>IF(U23&lt;0.1,"X",IF(U23&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X23" s="172">
+        <f>V23&amp;W23</f>
+        <v/>
+      </c>
+      <c r="Y23" s="173">
+        <f>E23*R23</f>
+        <v/>
+      </c>
+      <c r="Z23" s="174">
+        <f>Y23/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA23" s="175">
+        <f>IF(V23="A","✓ A-CLASS",IF(V23="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-AIR-003</t>
+        </is>
+      </c>
+      <c r="B24" s="177" t="inlineStr">
+        <is>
+          <t>Air Filter Element</t>
+        </is>
+      </c>
+      <c r="C24" s="178" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D24" s="178" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E24" s="179" t="n">
+        <v>60</v>
+      </c>
+      <c r="F24" s="165" t="n">
+        <v>107</v>
+      </c>
+      <c r="G24" s="165" t="n">
+        <v>103</v>
+      </c>
+      <c r="H24" s="165" t="n">
+        <v>119</v>
+      </c>
+      <c r="I24" s="165" t="n">
+        <v>147</v>
+      </c>
+      <c r="J24" s="165" t="n">
+        <v>107</v>
+      </c>
+      <c r="K24" s="165" t="n">
+        <v>126</v>
+      </c>
+      <c r="L24" s="165" t="n">
+        <v>125</v>
+      </c>
+      <c r="M24" s="165" t="n">
+        <v>129</v>
+      </c>
+      <c r="N24" s="165" t="n">
+        <v>124</v>
+      </c>
+      <c r="O24" s="165" t="n">
+        <v>129</v>
+      </c>
+      <c r="P24" s="165" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q24" s="165" t="n">
+        <v>140</v>
+      </c>
+      <c r="R24" s="166">
+        <f>SUM(F24:Q24)</f>
+        <v/>
+      </c>
+      <c r="S24" s="167">
+        <f>R24/12</f>
+        <v/>
+      </c>
+      <c r="T24" s="168">
+        <f>STDEV(F24:Q24)</f>
+        <v/>
+      </c>
+      <c r="U24" s="169">
+        <f>IF(S24=0,9999,T24/S24)</f>
+        <v/>
+      </c>
+      <c r="V24" s="170">
+        <f>IF(Z24&lt;=0.7,"A",IF(Z24&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W24" s="171">
+        <f>IF(U24&lt;0.1,"X",IF(U24&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X24" s="172">
+        <f>V24&amp;W24</f>
+        <v/>
+      </c>
+      <c r="Y24" s="173">
+        <f>E24*R24</f>
+        <v/>
+      </c>
+      <c r="Z24" s="174">
+        <f>Y24/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA24" s="175">
+        <f>IF(V24="A","✓ A-CLASS",IF(V24="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-BRK-036</t>
+        </is>
+      </c>
+      <c r="B25" s="162" t="inlineStr">
+        <is>
+          <t>Brake Pad Rear Set</t>
+        </is>
+      </c>
+      <c r="C25" s="163" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D25" s="163" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E25" s="164" t="n">
+        <v>80</v>
+      </c>
+      <c r="F25" s="165" t="n">
+        <v>84</v>
+      </c>
+      <c r="G25" s="165" t="n">
+        <v>97</v>
+      </c>
+      <c r="H25" s="165" t="n">
+        <v>80</v>
+      </c>
+      <c r="I25" s="165" t="n">
+        <v>81</v>
+      </c>
+      <c r="J25" s="165" t="n">
+        <v>98</v>
+      </c>
+      <c r="K25" s="165" t="n">
+        <v>80</v>
+      </c>
+      <c r="L25" s="165" t="n">
+        <v>99</v>
+      </c>
+      <c r="M25" s="165" t="n">
+        <v>83</v>
+      </c>
+      <c r="N25" s="165" t="n">
+        <v>77</v>
+      </c>
+      <c r="O25" s="165" t="n">
+        <v>97</v>
+      </c>
+      <c r="P25" s="165" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q25" s="165" t="n">
+        <v>87</v>
+      </c>
+      <c r="R25" s="166">
+        <f>SUM(F25:Q25)</f>
+        <v/>
+      </c>
+      <c r="S25" s="167">
+        <f>R25/12</f>
+        <v/>
+      </c>
+      <c r="T25" s="168">
+        <f>STDEV(F25:Q25)</f>
+        <v/>
+      </c>
+      <c r="U25" s="169">
+        <f>IF(S25=0,9999,T25/S25)</f>
+        <v/>
+      </c>
+      <c r="V25" s="170">
+        <f>IF(Z25&lt;=0.7,"A",IF(Z25&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W25" s="171">
+        <f>IF(U25&lt;0.1,"X",IF(U25&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X25" s="172">
+        <f>V25&amp;W25</f>
+        <v/>
+      </c>
+      <c r="Y25" s="173">
+        <f>E25*R25</f>
+        <v/>
+      </c>
+      <c r="Z25" s="174">
+        <f>Y25/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA25" s="175">
+        <f>IF(V25="A","✓ A-CLASS",IF(V25="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-OIL-002</t>
+        </is>
+      </c>
+      <c r="B26" s="177" t="inlineStr">
+        <is>
+          <t>Oil Filter Standard</t>
+        </is>
+      </c>
+      <c r="C26" s="178" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D26" s="178" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E26" s="179" t="n">
+        <v>45</v>
+      </c>
+      <c r="F26" s="165" t="n">
+        <v>144</v>
+      </c>
+      <c r="G26" s="165" t="n">
+        <v>166</v>
+      </c>
+      <c r="H26" s="165" t="n">
+        <v>144</v>
+      </c>
+      <c r="I26" s="165" t="n">
+        <v>158</v>
+      </c>
+      <c r="J26" s="165" t="n">
+        <v>151</v>
+      </c>
+      <c r="K26" s="165" t="n">
+        <v>144</v>
+      </c>
+      <c r="L26" s="165" t="n">
+        <v>164</v>
+      </c>
+      <c r="M26" s="165" t="n">
+        <v>165</v>
+      </c>
+      <c r="N26" s="165" t="n">
+        <v>159</v>
+      </c>
+      <c r="O26" s="165" t="n">
+        <v>142</v>
+      </c>
+      <c r="P26" s="165" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q26" s="165" t="n">
+        <v>147</v>
+      </c>
+      <c r="R26" s="166">
+        <f>SUM(F26:Q26)</f>
+        <v/>
+      </c>
+      <c r="S26" s="167">
+        <f>R26/12</f>
+        <v/>
+      </c>
+      <c r="T26" s="168">
+        <f>STDEV(F26:Q26)</f>
+        <v/>
+      </c>
+      <c r="U26" s="169">
+        <f>IF(S26=0,9999,T26/S26)</f>
+        <v/>
+      </c>
+      <c r="V26" s="170">
+        <f>IF(Z26&lt;=0.7,"A",IF(Z26&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W26" s="171">
+        <f>IF(U26&lt;0.1,"X",IF(U26&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X26" s="172">
+        <f>V26&amp;W26</f>
+        <v/>
+      </c>
+      <c r="Y26" s="173">
+        <f>E26*R26</f>
+        <v/>
+      </c>
+      <c r="Z26" s="174">
+        <f>Y26/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA26" s="175">
+        <f>IF(V26="A","✓ A-CLASS",IF(V26="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-DRV-022</t>
+        </is>
+      </c>
+      <c r="B27" s="162" t="inlineStr">
+        <is>
+          <t>Drive Shaft Front</t>
+        </is>
+      </c>
+      <c r="C27" s="163" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D27" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E27" s="164" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F27" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="166">
+        <f>SUM(F27:Q27)</f>
+        <v/>
+      </c>
+      <c r="S27" s="167">
+        <f>R27/12</f>
+        <v/>
+      </c>
+      <c r="T27" s="168">
+        <f>STDEV(F27:Q27)</f>
+        <v/>
+      </c>
+      <c r="U27" s="169">
+        <f>IF(S27=0,9999,T27/S27)</f>
+        <v/>
+      </c>
+      <c r="V27" s="170">
+        <f>IF(Z27&lt;=0.7,"A",IF(Z27&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W27" s="171">
+        <f>IF(U27&lt;0.1,"X",IF(U27&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X27" s="172">
+        <f>V27&amp;W27</f>
+        <v/>
+      </c>
+      <c r="Y27" s="173">
+        <f>E27*R27</f>
+        <v/>
+      </c>
+      <c r="Z27" s="174">
+        <f>Y27/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA27" s="175">
+        <f>IF(V27="A","✓ A-CLASS",IF(V27="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-LAM-046</t>
+        </is>
+      </c>
+      <c r="B28" s="177" t="inlineStr">
+        <is>
+          <t>Lambda Sensor</t>
+        </is>
+      </c>
+      <c r="C28" s="178" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D28" s="178" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E28" s="179" t="n">
+        <v>220</v>
+      </c>
+      <c r="F28" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="165" t="n">
+        <v>55</v>
+      </c>
+      <c r="H28" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="165" t="n">
+        <v>41</v>
+      </c>
+      <c r="K28" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="165" t="n">
+        <v>111</v>
+      </c>
+      <c r="N28" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="165" t="n">
+        <v>59</v>
+      </c>
+      <c r="P28" s="165" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q28" s="165" t="n">
+        <v>57</v>
+      </c>
+      <c r="R28" s="166">
+        <f>SUM(F28:Q28)</f>
+        <v/>
+      </c>
+      <c r="S28" s="167">
+        <f>R28/12</f>
+        <v/>
+      </c>
+      <c r="T28" s="168">
+        <f>STDEV(F28:Q28)</f>
+        <v/>
+      </c>
+      <c r="U28" s="169">
+        <f>IF(S28=0,9999,T28/S28)</f>
+        <v/>
+      </c>
+      <c r="V28" s="170">
+        <f>IF(Z28&lt;=0.7,"A",IF(Z28&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W28" s="171">
+        <f>IF(U28&lt;0.1,"X",IF(U28&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X28" s="172">
+        <f>V28&amp;W28</f>
+        <v/>
+      </c>
+      <c r="Y28" s="173">
+        <f>E28*R28</f>
+        <v/>
+      </c>
+      <c r="Z28" s="174">
+        <f>Y28/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA28" s="175">
+        <f>IF(V28="A","✓ A-CLASS",IF(V28="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-DPF-041</t>
+        </is>
+      </c>
+      <c r="B29" s="162" t="inlineStr">
+        <is>
+          <t>DPF Filter</t>
+        </is>
+      </c>
+      <c r="C29" s="163" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D29" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E29" s="164" t="n">
+        <v>4200</v>
+      </c>
+      <c r="F29" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="165" t="n">
+        <v>15</v>
+      </c>
+      <c r="M29" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="166">
+        <f>SUM(F29:Q29)</f>
+        <v/>
+      </c>
+      <c r="S29" s="167">
+        <f>R29/12</f>
+        <v/>
+      </c>
+      <c r="T29" s="168">
+        <f>STDEV(F29:Q29)</f>
+        <v/>
+      </c>
+      <c r="U29" s="169">
+        <f>IF(S29=0,9999,T29/S29)</f>
+        <v/>
+      </c>
+      <c r="V29" s="170">
+        <f>IF(Z29&lt;=0.7,"A",IF(Z29&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W29" s="171">
+        <f>IF(U29&lt;0.1,"X",IF(U29&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X29" s="172">
+        <f>V29&amp;W29</f>
+        <v/>
+      </c>
+      <c r="Y29" s="173">
+        <f>E29*R29</f>
+        <v/>
+      </c>
+      <c r="Z29" s="174">
+        <f>Y29/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA29" s="175">
+        <f>IF(V29="A","✓ A-CLASS",IF(V29="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-SPK-008</t>
+        </is>
+      </c>
+      <c r="B30" s="177" t="inlineStr">
+        <is>
+          <t>Spark Plug Set</t>
+        </is>
+      </c>
+      <c r="C30" s="178" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D30" s="178" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E30" s="179" t="n">
+        <v>30</v>
+      </c>
+      <c r="F30" s="165" t="n">
+        <v>194</v>
+      </c>
+      <c r="G30" s="165" t="n">
+        <v>210</v>
+      </c>
+      <c r="H30" s="165" t="n">
+        <v>201</v>
+      </c>
+      <c r="I30" s="165" t="n">
+        <v>205</v>
+      </c>
+      <c r="J30" s="165" t="n">
+        <v>198</v>
+      </c>
+      <c r="K30" s="165" t="n">
+        <v>239</v>
+      </c>
+      <c r="L30" s="165" t="n">
+        <v>187</v>
+      </c>
+      <c r="M30" s="165" t="n">
+        <v>197</v>
+      </c>
+      <c r="N30" s="165" t="n">
+        <v>212</v>
+      </c>
+      <c r="O30" s="165" t="n">
+        <v>217</v>
+      </c>
+      <c r="P30" s="165" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q30" s="165" t="n">
+        <v>227</v>
+      </c>
+      <c r="R30" s="166">
+        <f>SUM(F30:Q30)</f>
+        <v/>
+      </c>
+      <c r="S30" s="167">
+        <f>R30/12</f>
+        <v/>
+      </c>
+      <c r="T30" s="168">
+        <f>STDEV(F30:Q30)</f>
+        <v/>
+      </c>
+      <c r="U30" s="169">
+        <f>IF(S30=0,9999,T30/S30)</f>
+        <v/>
+      </c>
+      <c r="V30" s="170">
+        <f>IF(Z30&lt;=0.7,"A",IF(Z30&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W30" s="171">
+        <f>IF(U30&lt;0.1,"X",IF(U30&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X30" s="172">
+        <f>V30&amp;W30</f>
+        <v/>
+      </c>
+      <c r="Y30" s="173">
+        <f>E30*R30</f>
+        <v/>
+      </c>
+      <c r="Z30" s="174">
+        <f>Y30/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA30" s="175">
+        <f>IF(V30="A","✓ A-CLASS",IF(V30="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-INV-034</t>
+        </is>
+      </c>
+      <c r="B31" s="162" t="inlineStr">
+        <is>
+          <t>Inverter Module</t>
+        </is>
+      </c>
+      <c r="C31" s="163" t="inlineStr">
+        <is>
+          <t>eCanter</t>
+        </is>
+      </c>
+      <c r="D31" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E31" s="164" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F31" s="165" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="165" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="165" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="166">
+        <f>SUM(F31:Q31)</f>
+        <v/>
+      </c>
+      <c r="S31" s="167">
+        <f>R31/12</f>
+        <v/>
+      </c>
+      <c r="T31" s="168">
+        <f>STDEV(F31:Q31)</f>
+        <v/>
+      </c>
+      <c r="U31" s="169">
+        <f>IF(S31=0,9999,T31/S31)</f>
+        <v/>
+      </c>
+      <c r="V31" s="170">
+        <f>IF(Z31&lt;=0.7,"A",IF(Z31&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W31" s="171">
+        <f>IF(U31&lt;0.1,"X",IF(U31&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X31" s="172">
+        <f>V31&amp;W31</f>
+        <v/>
+      </c>
+      <c r="Y31" s="173">
+        <f>E31*R31</f>
+        <v/>
+      </c>
+      <c r="Z31" s="174">
+        <f>Y31/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA31" s="175">
+        <f>IF(V31="A","✓ A-CLASS",IF(V31="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-TRM-010</t>
+        </is>
+      </c>
+      <c r="B32" s="177" t="inlineStr">
+        <is>
+          <t>Thermostat Assy</t>
+        </is>
+      </c>
+      <c r="C32" s="178" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D32" s="178" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E32" s="179" t="n">
+        <v>95</v>
+      </c>
+      <c r="F32" s="165" t="n">
+        <v>68</v>
+      </c>
+      <c r="G32" s="165" t="n">
+        <v>47</v>
+      </c>
+      <c r="H32" s="165" t="n">
+        <v>52</v>
+      </c>
+      <c r="I32" s="165" t="n">
+        <v>49</v>
+      </c>
+      <c r="J32" s="165" t="n">
+        <v>52</v>
+      </c>
+      <c r="K32" s="165" t="n">
+        <v>36</v>
+      </c>
+      <c r="L32" s="165" t="n">
+        <v>64</v>
+      </c>
+      <c r="M32" s="165" t="n">
+        <v>50</v>
+      </c>
+      <c r="N32" s="165" t="n">
+        <v>68</v>
+      </c>
+      <c r="O32" s="165" t="n">
+        <v>44</v>
+      </c>
+      <c r="P32" s="165" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q32" s="165" t="n">
+        <v>65</v>
+      </c>
+      <c r="R32" s="166">
+        <f>SUM(F32:Q32)</f>
+        <v/>
+      </c>
+      <c r="S32" s="167">
+        <f>R32/12</f>
+        <v/>
+      </c>
+      <c r="T32" s="168">
+        <f>STDEV(F32:Q32)</f>
+        <v/>
+      </c>
+      <c r="U32" s="169">
+        <f>IF(S32=0,9999,T32/S32)</f>
+        <v/>
+      </c>
+      <c r="V32" s="170">
+        <f>IF(Z32&lt;=0.7,"A",IF(Z32&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W32" s="171">
+        <f>IF(U32&lt;0.1,"X",IF(U32&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X32" s="172">
+        <f>V32&amp;W32</f>
+        <v/>
+      </c>
+      <c r="Y32" s="173">
+        <f>E32*R32</f>
+        <v/>
+      </c>
+      <c r="Z32" s="174">
+        <f>Y32/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA32" s="175">
+        <f>IF(V32="A","✓ A-CLASS",IF(V32="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-ACP-023</t>
+        </is>
+      </c>
+      <c r="B33" s="162" t="inlineStr">
+        <is>
+          <t>A/C Compressor</t>
+        </is>
+      </c>
+      <c r="C33" s="163" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D33" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E33" s="164" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F33" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="165" t="n">
+        <v>24</v>
+      </c>
+      <c r="L33" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="166">
+        <f>SUM(F33:Q33)</f>
+        <v/>
+      </c>
+      <c r="S33" s="167">
+        <f>R33/12</f>
+        <v/>
+      </c>
+      <c r="T33" s="168">
+        <f>STDEV(F33:Q33)</f>
+        <v/>
+      </c>
+      <c r="U33" s="169">
+        <f>IF(S33=0,9999,T33/S33)</f>
+        <v/>
+      </c>
+      <c r="V33" s="170">
+        <f>IF(Z33&lt;=0.7,"A",IF(Z33&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W33" s="171">
+        <f>IF(U33&lt;0.1,"X",IF(U33&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X33" s="172">
+        <f>V33&amp;W33</f>
+        <v/>
+      </c>
+      <c r="Y33" s="173">
+        <f>E33*R33</f>
+        <v/>
+      </c>
+      <c r="Z33" s="174">
+        <f>Y33/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA33" s="175">
+        <f>IF(V33="A","✓ A-CLASS",IF(V33="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-ADB-044</t>
+        </is>
+      </c>
+      <c r="B34" s="177" t="inlineStr">
+        <is>
+          <t>AdBlue Pump</t>
+        </is>
+      </c>
+      <c r="C34" s="178" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D34" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E34" s="179" t="n">
+        <v>640</v>
+      </c>
+      <c r="F34" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="165" t="n">
+        <v>79</v>
+      </c>
+      <c r="M34" s="165" t="n">
+        <v>17</v>
+      </c>
+      <c r="N34" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="166">
+        <f>SUM(F34:Q34)</f>
+        <v/>
+      </c>
+      <c r="S34" s="167">
+        <f>R34/12</f>
+        <v/>
+      </c>
+      <c r="T34" s="168">
+        <f>STDEV(F34:Q34)</f>
+        <v/>
+      </c>
+      <c r="U34" s="169">
+        <f>IF(S34=0,9999,T34/S34)</f>
+        <v/>
+      </c>
+      <c r="V34" s="170">
+        <f>IF(Z34&lt;=0.7,"A",IF(Z34&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W34" s="171">
+        <f>IF(U34&lt;0.1,"X",IF(U34&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X34" s="172">
+        <f>V34&amp;W34</f>
+        <v/>
+      </c>
+      <c r="Y34" s="173">
+        <f>E34*R34</f>
+        <v/>
+      </c>
+      <c r="Z34" s="174">
+        <f>Y34/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA34" s="175">
+        <f>IF(V34="A","✓ A-CLASS",IF(V34="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-BRH-019</t>
+        </is>
+      </c>
+      <c r="B35" s="162" t="inlineStr">
+        <is>
+          <t>Brake Hose Set</t>
+        </is>
+      </c>
+      <c r="C35" s="163" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D35" s="163" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E35" s="164" t="n">
+        <v>140</v>
+      </c>
+      <c r="F35" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="165" t="n">
+        <v>65</v>
+      </c>
+      <c r="H35" s="165" t="n">
+        <v>82</v>
+      </c>
+      <c r="I35" s="165" t="n">
+        <v>65</v>
+      </c>
+      <c r="J35" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="165" t="n">
+        <v>90</v>
+      </c>
+      <c r="M35" s="165" t="n">
+        <v>63</v>
+      </c>
+      <c r="N35" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="165" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q35" s="165" t="n">
+        <v>77</v>
+      </c>
+      <c r="R35" s="166">
+        <f>SUM(F35:Q35)</f>
+        <v/>
+      </c>
+      <c r="S35" s="167">
+        <f>R35/12</f>
+        <v/>
+      </c>
+      <c r="T35" s="168">
+        <f>STDEV(F35:Q35)</f>
+        <v/>
+      </c>
+      <c r="U35" s="169">
+        <f>IF(S35=0,9999,T35/S35)</f>
+        <v/>
+      </c>
+      <c r="V35" s="170">
+        <f>IF(Z35&lt;=0.7,"A",IF(Z35&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W35" s="171">
+        <f>IF(U35&lt;0.1,"X",IF(U35&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X35" s="172">
+        <f>V35&amp;W35</f>
+        <v/>
+      </c>
+      <c r="Y35" s="173">
+        <f>E35*R35</f>
+        <v/>
+      </c>
+      <c r="Z35" s="174">
+        <f>Y35/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA35" s="175">
+        <f>IF(V35="A","✓ A-CLASS",IF(V35="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-AIR-038</t>
+        </is>
+      </c>
+      <c r="B36" s="177" t="inlineStr">
+        <is>
+          <t>Air Filter HD</t>
+        </is>
+      </c>
+      <c r="C36" s="178" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D36" s="178" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E36" s="179" t="n">
+        <v>70</v>
+      </c>
+      <c r="F36" s="165" t="n">
+        <v>74</v>
+      </c>
+      <c r="G36" s="165" t="n">
+        <v>63</v>
+      </c>
+      <c r="H36" s="165" t="n">
+        <v>85</v>
+      </c>
+      <c r="I36" s="165" t="n">
+        <v>66</v>
+      </c>
+      <c r="J36" s="165" t="n">
+        <v>76</v>
+      </c>
+      <c r="K36" s="165" t="n">
+        <v>61</v>
+      </c>
+      <c r="L36" s="165" t="n">
+        <v>63</v>
+      </c>
+      <c r="M36" s="165" t="n">
+        <v>62</v>
+      </c>
+      <c r="N36" s="165" t="n">
+        <v>66</v>
+      </c>
+      <c r="O36" s="165" t="n">
+        <v>58</v>
+      </c>
+      <c r="P36" s="165" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q36" s="165" t="n">
+        <v>68</v>
+      </c>
+      <c r="R36" s="166">
+        <f>SUM(F36:Q36)</f>
+        <v/>
+      </c>
+      <c r="S36" s="167">
+        <f>R36/12</f>
+        <v/>
+      </c>
+      <c r="T36" s="168">
+        <f>STDEV(F36:Q36)</f>
+        <v/>
+      </c>
+      <c r="U36" s="169">
+        <f>IF(S36=0,9999,T36/S36)</f>
+        <v/>
+      </c>
+      <c r="V36" s="170">
+        <f>IF(Z36&lt;=0.7,"A",IF(Z36&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W36" s="171">
+        <f>IF(U36&lt;0.1,"X",IF(U36&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X36" s="172">
+        <f>V36&amp;W36</f>
+        <v/>
+      </c>
+      <c r="Y36" s="173">
+        <f>E36*R36</f>
+        <v/>
+      </c>
+      <c r="Z36" s="174">
+        <f>Y36/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA36" s="175">
+        <f>IF(V36="A","✓ A-CLASS",IF(V36="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-RAD-009</t>
+        </is>
+      </c>
+      <c r="B37" s="162" t="inlineStr">
+        <is>
+          <t>Radiator Hose Upper</t>
+        </is>
+      </c>
+      <c r="C37" s="163" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D37" s="163" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E37" s="164" t="n">
+        <v>75</v>
+      </c>
+      <c r="F37" s="165" t="n">
+        <v>54</v>
+      </c>
+      <c r="G37" s="165" t="n">
+        <v>68</v>
+      </c>
+      <c r="H37" s="165" t="n">
+        <v>61</v>
+      </c>
+      <c r="I37" s="165" t="n">
+        <v>59</v>
+      </c>
+      <c r="J37" s="165" t="n">
+        <v>68</v>
+      </c>
+      <c r="K37" s="165" t="n">
+        <v>53</v>
+      </c>
+      <c r="L37" s="165" t="n">
+        <v>58</v>
+      </c>
+      <c r="M37" s="165" t="n">
+        <v>57</v>
+      </c>
+      <c r="N37" s="165" t="n">
+        <v>57</v>
+      </c>
+      <c r="O37" s="165" t="n">
+        <v>76</v>
+      </c>
+      <c r="P37" s="165" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q37" s="165" t="n">
+        <v>52</v>
+      </c>
+      <c r="R37" s="166">
+        <f>SUM(F37:Q37)</f>
+        <v/>
+      </c>
+      <c r="S37" s="167">
+        <f>R37/12</f>
+        <v/>
+      </c>
+      <c r="T37" s="168">
+        <f>STDEV(F37:Q37)</f>
+        <v/>
+      </c>
+      <c r="U37" s="169">
+        <f>IF(S37=0,9999,T37/S37)</f>
+        <v/>
+      </c>
+      <c r="V37" s="170">
+        <f>IF(Z37&lt;=0.7,"A",IF(Z37&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W37" s="171">
+        <f>IF(U37&lt;0.1,"X",IF(U37&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X37" s="172">
+        <f>V37&amp;W37</f>
+        <v/>
+      </c>
+      <c r="Y37" s="173">
+        <f>E37*R37</f>
+        <v/>
+      </c>
+      <c r="Z37" s="174">
+        <f>Y37/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA37" s="175">
+        <f>IF(V37="A","✓ A-CLASS",IF(V37="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-HDG-024</t>
+        </is>
+      </c>
+      <c r="B38" s="177" t="inlineStr">
+        <is>
+          <t>Head Gasket Set</t>
+        </is>
+      </c>
+      <c r="C38" s="178" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D38" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E38" s="179" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F38" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="165" t="n">
+        <v>13</v>
+      </c>
+      <c r="H38" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="165" t="n">
+        <v>15</v>
+      </c>
+      <c r="L38" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="165" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q38" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="166">
+        <f>SUM(F38:Q38)</f>
+        <v/>
+      </c>
+      <c r="S38" s="167">
+        <f>R38/12</f>
+        <v/>
+      </c>
+      <c r="T38" s="168">
+        <f>STDEV(F38:Q38)</f>
+        <v/>
+      </c>
+      <c r="U38" s="169">
+        <f>IF(S38=0,9999,T38/S38)</f>
+        <v/>
+      </c>
+      <c r="V38" s="170">
+        <f>IF(Z38&lt;=0.7,"A",IF(Z38&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W38" s="171">
+        <f>IF(U38&lt;0.1,"X",IF(U38&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X38" s="172">
+        <f>V38&amp;W38</f>
+        <v/>
+      </c>
+      <c r="Y38" s="173">
+        <f>E38*R38</f>
+        <v/>
+      </c>
+      <c r="Z38" s="174">
+        <f>Y38/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA38" s="175">
+        <f>IF(V38="A","✓ A-CLASS",IF(V38="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-FLT-048</t>
+        </is>
+      </c>
+      <c r="B39" s="162" t="inlineStr">
+        <is>
+          <t>Fuel Filter</t>
+        </is>
+      </c>
+      <c r="C39" s="163" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D39" s="163" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E39" s="164" t="n">
+        <v>55</v>
+      </c>
+      <c r="F39" s="165" t="n">
+        <v>100</v>
+      </c>
+      <c r="G39" s="165" t="n">
+        <v>95</v>
+      </c>
+      <c r="H39" s="165" t="n">
+        <v>67</v>
+      </c>
+      <c r="I39" s="165" t="n">
+        <v>85</v>
+      </c>
+      <c r="J39" s="165" t="n">
+        <v>82</v>
+      </c>
+      <c r="K39" s="165" t="n">
+        <v>89</v>
+      </c>
+      <c r="L39" s="165" t="n">
+        <v>72</v>
+      </c>
+      <c r="M39" s="165" t="n">
+        <v>88</v>
+      </c>
+      <c r="N39" s="165" t="n">
+        <v>86</v>
+      </c>
+      <c r="O39" s="165" t="n">
+        <v>95</v>
+      </c>
+      <c r="P39" s="165" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q39" s="165" t="n">
+        <v>74</v>
+      </c>
+      <c r="R39" s="166">
+        <f>SUM(F39:Q39)</f>
+        <v/>
+      </c>
+      <c r="S39" s="167">
+        <f>R39/12</f>
+        <v/>
+      </c>
+      <c r="T39" s="168">
+        <f>STDEV(F39:Q39)</f>
+        <v/>
+      </c>
+      <c r="U39" s="169">
+        <f>IF(S39=0,9999,T39/S39)</f>
+        <v/>
+      </c>
+      <c r="V39" s="170">
+        <f>IF(Z39&lt;=0.7,"A",IF(Z39&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W39" s="171">
+        <f>IF(U39&lt;0.1,"X",IF(U39&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X39" s="172">
+        <f>V39&amp;W39</f>
+        <v/>
+      </c>
+      <c r="Y39" s="173">
+        <f>E39*R39</f>
+        <v/>
+      </c>
+      <c r="Z39" s="174">
+        <f>Y39/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA39" s="175">
+        <f>IF(V39="A","✓ A-CLASS",IF(V39="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-OIL-037</t>
+        </is>
+      </c>
+      <c r="B40" s="177" t="inlineStr">
+        <is>
+          <t>Oil Filter HD</t>
+        </is>
+      </c>
+      <c r="C40" s="178" t="inlineStr">
+        <is>
+          <t>Fighter FM</t>
+        </is>
+      </c>
+      <c r="D40" s="178" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E40" s="179" t="n">
+        <v>55</v>
+      </c>
+      <c r="F40" s="165" t="n">
+        <v>70</v>
+      </c>
+      <c r="G40" s="165" t="n">
+        <v>66</v>
+      </c>
+      <c r="H40" s="165" t="n">
+        <v>64</v>
+      </c>
+      <c r="I40" s="165" t="n">
+        <v>58</v>
+      </c>
+      <c r="J40" s="165" t="n">
+        <v>73</v>
+      </c>
+      <c r="K40" s="165" t="n">
+        <v>79</v>
+      </c>
+      <c r="L40" s="165" t="n">
+        <v>69</v>
+      </c>
+      <c r="M40" s="165" t="n">
+        <v>68</v>
+      </c>
+      <c r="N40" s="165" t="n">
+        <v>59</v>
+      </c>
+      <c r="O40" s="165" t="n">
+        <v>86</v>
+      </c>
+      <c r="P40" s="165" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q40" s="165" t="n">
+        <v>62</v>
+      </c>
+      <c r="R40" s="166">
+        <f>SUM(F40:Q40)</f>
+        <v/>
+      </c>
+      <c r="S40" s="167">
+        <f>R40/12</f>
+        <v/>
+      </c>
+      <c r="T40" s="168">
+        <f>STDEV(F40:Q40)</f>
+        <v/>
+      </c>
+      <c r="U40" s="169">
+        <f>IF(S40=0,9999,T40/S40)</f>
+        <v/>
+      </c>
+      <c r="V40" s="170">
+        <f>IF(Z40&lt;=0.7,"A",IF(Z40&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W40" s="171">
+        <f>IF(U40&lt;0.1,"X",IF(U40&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X40" s="172">
+        <f>V40&amp;W40</f>
+        <v/>
+      </c>
+      <c r="Y40" s="173">
+        <f>E40*R40</f>
+        <v/>
+      </c>
+      <c r="Z40" s="174">
+        <f>Y40/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA40" s="175">
+        <f>IF(V40="A","✓ A-CLASS",IF(V40="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-CPM-033</t>
+        </is>
+      </c>
+      <c r="B41" s="162" t="inlineStr">
+        <is>
+          <t>Coolant Pump EV</t>
+        </is>
+      </c>
+      <c r="C41" s="163" t="inlineStr">
+        <is>
+          <t>eCanter</t>
+        </is>
+      </c>
+      <c r="D41" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E41" s="164" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F41" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="165" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="165" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" s="165" t="n">
+        <v>7</v>
+      </c>
+      <c r="L41" s="165" t="n">
+        <v>8</v>
+      </c>
+      <c r="M41" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="166">
+        <f>SUM(F41:Q41)</f>
+        <v/>
+      </c>
+      <c r="S41" s="167">
+        <f>R41/12</f>
+        <v/>
+      </c>
+      <c r="T41" s="168">
+        <f>STDEV(F41:Q41)</f>
+        <v/>
+      </c>
+      <c r="U41" s="169">
+        <f>IF(S41=0,9999,T41/S41)</f>
+        <v/>
+      </c>
+      <c r="V41" s="170">
+        <f>IF(Z41&lt;=0.7,"A",IF(Z41&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W41" s="171">
+        <f>IF(U41&lt;0.1,"X",IF(U41&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X41" s="172">
+        <f>V41&amp;W41</f>
+        <v/>
+      </c>
+      <c r="Y41" s="173">
+        <f>E41*R41</f>
+        <v/>
+      </c>
+      <c r="Z41" s="174">
+        <f>Y41/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA41" s="175">
+        <f>IF(V41="A","✓ A-CLASS",IF(V41="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-SCR-043</t>
+        </is>
+      </c>
+      <c r="B42" s="177" t="inlineStr">
+        <is>
+          <t>SCR Catalyst</t>
+        </is>
+      </c>
+      <c r="C42" s="178" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D42" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E42" s="179" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F42" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="165" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="165" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="165" t="n">
+        <v>5</v>
+      </c>
+      <c r="O42" s="165" t="n">
+        <v>4</v>
+      </c>
+      <c r="P42" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="166">
+        <f>SUM(F42:Q42)</f>
+        <v/>
+      </c>
+      <c r="S42" s="167">
+        <f>R42/12</f>
+        <v/>
+      </c>
+      <c r="T42" s="168">
+        <f>STDEV(F42:Q42)</f>
+        <v/>
+      </c>
+      <c r="U42" s="169">
+        <f>IF(S42=0,9999,T42/S42)</f>
+        <v/>
+      </c>
+      <c r="V42" s="170">
+        <f>IF(Z42&lt;=0.7,"A",IF(Z42&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W42" s="171">
+        <f>IF(U42&lt;0.1,"X",IF(U42&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X42" s="172">
+        <f>V42&amp;W42</f>
+        <v/>
+      </c>
+      <c r="Y42" s="173">
+        <f>E42*R42</f>
+        <v/>
+      </c>
+      <c r="Z42" s="174">
+        <f>Y42/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA42" s="175">
+        <f>IF(V42="A","✓ A-CLASS",IF(V42="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-CHG-035</t>
+        </is>
+      </c>
+      <c r="B43" s="162" t="inlineStr">
+        <is>
+          <t>On-Board Charger</t>
+        </is>
+      </c>
+      <c r="C43" s="163" t="inlineStr">
+        <is>
+          <t>eCanter</t>
+        </is>
+      </c>
+      <c r="D43" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E43" s="164" t="n">
+        <v>9500</v>
+      </c>
+      <c r="F43" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="165" t="n">
+        <v>4</v>
+      </c>
+      <c r="N43" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="166">
+        <f>SUM(F43:Q43)</f>
+        <v/>
+      </c>
+      <c r="S43" s="167">
+        <f>R43/12</f>
+        <v/>
+      </c>
+      <c r="T43" s="168">
+        <f>STDEV(F43:Q43)</f>
+        <v/>
+      </c>
+      <c r="U43" s="169">
+        <f>IF(S43=0,9999,T43/S43)</f>
+        <v/>
+      </c>
+      <c r="V43" s="170">
+        <f>IF(Z43&lt;=0.7,"A",IF(Z43&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W43" s="171">
+        <f>IF(U43&lt;0.1,"X",IF(U43&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X43" s="172">
+        <f>V43&amp;W43</f>
+        <v/>
+      </c>
+      <c r="Y43" s="173">
+        <f>E43*R43</f>
+        <v/>
+      </c>
+      <c r="Z43" s="174">
+        <f>Y43/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA43" s="175">
+        <f>IF(V43="A","✓ A-CLASS",IF(V43="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-TIM-028</t>
+        </is>
+      </c>
+      <c r="B44" s="177" t="inlineStr">
+        <is>
+          <t>Timing Chain Kit</t>
+        </is>
+      </c>
+      <c r="C44" s="178" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D44" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E44" s="179" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F44" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="165" t="n">
+        <v>11</v>
+      </c>
+      <c r="H44" s="165" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="165" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="166">
+        <f>SUM(F44:Q44)</f>
+        <v/>
+      </c>
+      <c r="S44" s="167">
+        <f>R44/12</f>
+        <v/>
+      </c>
+      <c r="T44" s="168">
+        <f>STDEV(F44:Q44)</f>
+        <v/>
+      </c>
+      <c r="U44" s="169">
+        <f>IF(S44=0,9999,T44/S44)</f>
+        <v/>
+      </c>
+      <c r="V44" s="170">
+        <f>IF(Z44&lt;=0.7,"A",IF(Z44&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W44" s="171">
+        <f>IF(U44&lt;0.1,"X",IF(U44&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X44" s="172">
+        <f>V44&amp;W44</f>
+        <v/>
+      </c>
+      <c r="Y44" s="173">
+        <f>E44*R44</f>
+        <v/>
+      </c>
+      <c r="Z44" s="174">
+        <f>Y44/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA44" s="175">
+        <f>IF(V44="A","✓ A-CLASS",IF(V44="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-PCV-047</t>
+        </is>
+      </c>
+      <c r="B45" s="162" t="inlineStr">
+        <is>
+          <t>PCV Valve</t>
+        </is>
+      </c>
+      <c r="C45" s="163" t="inlineStr">
+        <is>
+          <t>Canter FE</t>
+        </is>
+      </c>
+      <c r="D45" s="163" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E45" s="164" t="n">
+        <v>45</v>
+      </c>
+      <c r="F45" s="165" t="n">
+        <v>55</v>
+      </c>
+      <c r="G45" s="165" t="n">
+        <v>57</v>
+      </c>
+      <c r="H45" s="165" t="n">
+        <v>69</v>
+      </c>
+      <c r="I45" s="165" t="n">
+        <v>67</v>
+      </c>
+      <c r="J45" s="165" t="n">
+        <v>66</v>
+      </c>
+      <c r="K45" s="165" t="n">
+        <v>60</v>
+      </c>
+      <c r="L45" s="165" t="n">
+        <v>54</v>
+      </c>
+      <c r="M45" s="165" t="n">
+        <v>59</v>
+      </c>
+      <c r="N45" s="165" t="n">
+        <v>59</v>
+      </c>
+      <c r="O45" s="165" t="n">
+        <v>54</v>
+      </c>
+      <c r="P45" s="165" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q45" s="165" t="n">
+        <v>84</v>
+      </c>
+      <c r="R45" s="166">
+        <f>SUM(F45:Q45)</f>
+        <v/>
+      </c>
+      <c r="S45" s="167">
+        <f>R45/12</f>
+        <v/>
+      </c>
+      <c r="T45" s="168">
+        <f>STDEV(F45:Q45)</f>
+        <v/>
+      </c>
+      <c r="U45" s="169">
+        <f>IF(S45=0,9999,T45/S45)</f>
+        <v/>
+      </c>
+      <c r="V45" s="170">
+        <f>IF(Z45&lt;=0.7,"A",IF(Z45&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W45" s="171">
+        <f>IF(U45&lt;0.1,"X",IF(U45&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X45" s="172">
+        <f>V45&amp;W45</f>
+        <v/>
+      </c>
+      <c r="Y45" s="173">
+        <f>E45*R45</f>
+        <v/>
+      </c>
+      <c r="Z45" s="174">
+        <f>Y45/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA45" s="175">
+        <f>IF(V45="A","✓ A-CLASS",IF(V45="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-CRK-025</t>
+        </is>
+      </c>
+      <c r="B46" s="177" t="inlineStr">
+        <is>
+          <t>Crankshaft Seal Kit</t>
+        </is>
+      </c>
+      <c r="C46" s="178" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D46" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E46" s="179" t="n">
+        <v>650</v>
+      </c>
+      <c r="F46" s="165" t="n">
+        <v>42</v>
+      </c>
+      <c r="G46" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="166">
+        <f>SUM(F46:Q46)</f>
+        <v/>
+      </c>
+      <c r="S46" s="167">
+        <f>R46/12</f>
+        <v/>
+      </c>
+      <c r="T46" s="168">
+        <f>STDEV(F46:Q46)</f>
+        <v/>
+      </c>
+      <c r="U46" s="169">
+        <f>IF(S46=0,9999,T46/S46)</f>
+        <v/>
+      </c>
+      <c r="V46" s="170">
+        <f>IF(Z46&lt;=0.7,"A",IF(Z46&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W46" s="171">
+        <f>IF(U46&lt;0.1,"X",IF(U46&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X46" s="172">
+        <f>V46&amp;W46</f>
+        <v/>
+      </c>
+      <c r="Y46" s="173">
+        <f>E46*R46</f>
+        <v/>
+      </c>
+      <c r="Z46" s="174">
+        <f>Y46/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA46" s="175">
+        <f>IF(V46="A","✓ A-CLASS",IF(V46="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-CAM-026</t>
+        </is>
+      </c>
+      <c r="B47" s="162" t="inlineStr">
+        <is>
+          <t>Camshaft Bearing</t>
+        </is>
+      </c>
+      <c r="C47" s="163" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D47" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E47" s="164" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F47" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="165" t="n">
+        <v>18</v>
+      </c>
+      <c r="H47" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="166">
+        <f>SUM(F47:Q47)</f>
+        <v/>
+      </c>
+      <c r="S47" s="167">
+        <f>R47/12</f>
+        <v/>
+      </c>
+      <c r="T47" s="168">
+        <f>STDEV(F47:Q47)</f>
+        <v/>
+      </c>
+      <c r="U47" s="169">
+        <f>IF(S47=0,9999,T47/S47)</f>
+        <v/>
+      </c>
+      <c r="V47" s="170">
+        <f>IF(Z47&lt;=0.7,"A",IF(Z47&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W47" s="171">
+        <f>IF(U47&lt;0.1,"X",IF(U47&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X47" s="172">
+        <f>V47&amp;W47</f>
+        <v/>
+      </c>
+      <c r="Y47" s="173">
+        <f>E47*R47</f>
+        <v/>
+      </c>
+      <c r="Z47" s="174">
+        <f>Y47/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA47" s="175">
+        <f>IF(V47="A","✓ A-CLASS",IF(V47="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-PIS-030</t>
+        </is>
+      </c>
+      <c r="B48" s="177" t="inlineStr">
+        <is>
+          <t>Piston Ring Set</t>
+        </is>
+      </c>
+      <c r="C48" s="178" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D48" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E48" s="179" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F48" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="165" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" s="165" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="165" t="n">
+        <v>2</v>
+      </c>
+      <c r="P48" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="166">
+        <f>SUM(F48:Q48)</f>
+        <v/>
+      </c>
+      <c r="S48" s="167">
+        <f>R48/12</f>
+        <v/>
+      </c>
+      <c r="T48" s="168">
+        <f>STDEV(F48:Q48)</f>
+        <v/>
+      </c>
+      <c r="U48" s="169">
+        <f>IF(S48=0,9999,T48/S48)</f>
+        <v/>
+      </c>
+      <c r="V48" s="170">
+        <f>IF(Z48&lt;=0.7,"A",IF(Z48&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W48" s="171">
+        <f>IF(U48&lt;0.1,"X",IF(U48&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X48" s="172">
+        <f>V48&amp;W48</f>
+        <v/>
+      </c>
+      <c r="Y48" s="173">
+        <f>E48*R48</f>
+        <v/>
+      </c>
+      <c r="Z48" s="174">
+        <f>Y48/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA48" s="175">
+        <f>IF(V48="A","✓ A-CLASS",IF(V48="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-NOX-042</t>
+        </is>
+      </c>
+      <c r="B49" s="162" t="inlineStr">
+        <is>
+          <t>NOx Sensor</t>
+        </is>
+      </c>
+      <c r="C49" s="163" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D49" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E49" s="164" t="n">
+        <v>780</v>
+      </c>
+      <c r="F49" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="165" t="n">
+        <v>5</v>
+      </c>
+      <c r="I49" s="165" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" s="165" t="n">
+        <v>17</v>
+      </c>
+      <c r="K49" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="166">
+        <f>SUM(F49:Q49)</f>
+        <v/>
+      </c>
+      <c r="S49" s="167">
+        <f>R49/12</f>
+        <v/>
+      </c>
+      <c r="T49" s="168">
+        <f>STDEV(F49:Q49)</f>
+        <v/>
+      </c>
+      <c r="U49" s="169">
+        <f>IF(S49=0,9999,T49/S49)</f>
+        <v/>
+      </c>
+      <c r="V49" s="170">
+        <f>IF(Z49&lt;=0.7,"A",IF(Z49&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W49" s="171">
+        <f>IF(U49&lt;0.1,"X",IF(U49&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X49" s="172">
+        <f>V49&amp;W49</f>
+        <v/>
+      </c>
+      <c r="Y49" s="173">
+        <f>E49*R49</f>
+        <v/>
+      </c>
+      <c r="Z49" s="174">
+        <f>Y49/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA49" s="175">
+        <f>IF(V49="A","✓ A-CLASS",IF(V49="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-OPS-027</t>
+        </is>
+      </c>
+      <c r="B50" s="177" t="inlineStr">
+        <is>
+          <t>Oil Pan Gasket</t>
+        </is>
+      </c>
+      <c r="C50" s="178" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D50" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E50" s="179" t="n">
+        <v>380</v>
+      </c>
+      <c r="F50" s="165" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="165" t="n">
+        <v>3</v>
+      </c>
+      <c r="N50" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="165" t="n">
+        <v>22</v>
+      </c>
+      <c r="P50" s="165" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q50" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="166">
+        <f>SUM(F50:Q50)</f>
+        <v/>
+      </c>
+      <c r="S50" s="167">
+        <f>R50/12</f>
+        <v/>
+      </c>
+      <c r="T50" s="168">
+        <f>STDEV(F50:Q50)</f>
+        <v/>
+      </c>
+      <c r="U50" s="169">
+        <f>IF(S50=0,9999,T50/S50)</f>
+        <v/>
+      </c>
+      <c r="V50" s="170">
+        <f>IF(Z50&lt;=0.7,"A",IF(Z50&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W50" s="171">
+        <f>IF(U50&lt;0.1,"X",IF(U50&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X50" s="172">
+        <f>V50&amp;W50</f>
+        <v/>
+      </c>
+      <c r="Y50" s="173">
+        <f>E50*R50</f>
+        <v/>
+      </c>
+      <c r="Z50" s="174">
+        <f>Y50/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA50" s="175">
+        <f>IF(V50="A","✓ A-CLASS",IF(V50="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="161" t="inlineStr">
+        <is>
+          <t>FUSO-VLV-029</t>
+        </is>
+      </c>
+      <c r="B51" s="162" t="inlineStr">
+        <is>
+          <t>Valve Cover Gasket</t>
+        </is>
+      </c>
+      <c r="C51" s="163" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D51" s="163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E51" s="164" t="n">
+        <v>420</v>
+      </c>
+      <c r="F51" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="165" t="n">
+        <v>3</v>
+      </c>
+      <c r="N51" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="165" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q51" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="166">
+        <f>SUM(F51:Q51)</f>
+        <v/>
+      </c>
+      <c r="S51" s="167">
+        <f>R51/12</f>
+        <v/>
+      </c>
+      <c r="T51" s="168">
+        <f>STDEV(F51:Q51)</f>
+        <v/>
+      </c>
+      <c r="U51" s="169">
+        <f>IF(S51=0,9999,T51/S51)</f>
+        <v/>
+      </c>
+      <c r="V51" s="170">
+        <f>IF(Z51&lt;=0.7,"A",IF(Z51&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W51" s="171">
+        <f>IF(U51&lt;0.1,"X",IF(U51&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X51" s="172">
+        <f>V51&amp;W51</f>
+        <v/>
+      </c>
+      <c r="Y51" s="173">
+        <f>E51*R51</f>
+        <v/>
+      </c>
+      <c r="Z51" s="174">
+        <f>Y51/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA51" s="175">
+        <f>IF(V51="A","✓ A-CLASS",IF(V51="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="176" t="inlineStr">
+        <is>
+          <t>FUSO-GKT-039</t>
+        </is>
+      </c>
+      <c r="B52" s="177" t="inlineStr">
+        <is>
+          <t>Rocker Cover Gasket</t>
+        </is>
+      </c>
+      <c r="C52" s="178" t="inlineStr">
+        <is>
+          <t>Super Great V</t>
+        </is>
+      </c>
+      <c r="D52" s="178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E52" s="179" t="n">
+        <v>280</v>
+      </c>
+      <c r="F52" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="165" t="n">
+        <v>4</v>
+      </c>
+      <c r="K52" s="165" t="n">
+        <v>26</v>
+      </c>
+      <c r="L52" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="166">
+        <f>SUM(F52:Q52)</f>
+        <v/>
+      </c>
+      <c r="S52" s="167">
+        <f>R52/12</f>
+        <v/>
+      </c>
+      <c r="T52" s="168">
+        <f>STDEV(F52:Q52)</f>
+        <v/>
+      </c>
+      <c r="U52" s="169">
+        <f>IF(S52=0,9999,T52/S52)</f>
+        <v/>
+      </c>
+      <c r="V52" s="170">
+        <f>IF(Z52&lt;=0.7,"A",IF(Z52&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="W52" s="171">
+        <f>IF(U52&lt;0.1,"X",IF(U52&lt;0.3,"Y","Z"))</f>
+        <v/>
+      </c>
+      <c r="X52" s="172">
+        <f>V52&amp;W52</f>
+        <v/>
+      </c>
+      <c r="Y52" s="173">
+        <f>E52*R52</f>
+        <v/>
+      </c>
+      <c r="Z52" s="174">
+        <f>Y52/SUM($Y$3:$Y$52)</f>
+        <v/>
+      </c>
+      <c r="AA52" s="175">
+        <f>IF(V52="A","✓ A-CLASS",IF(V52="B","✓ B-CLASS","✓ C-CLASS"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="181" t="inlineStr">
+        <is>
+          <t>HOW TO READ THIS SHEET — Formula Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="182" t="inlineStr">
+        <is>
+          <t>Col F–Q</t>
+        </is>
+      </c>
+      <c r="B55" s="183" t="inlineStr">
+        <is>
+          <t>Raw monthly demand units for Apr-25 to Mar-26. Blue = demand occurred. Red = zero demand month (potential stockout or genuine zero).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="182" t="inlineStr">
+        <is>
+          <t>Col R (Annual Demand)</t>
+        </is>
+      </c>
+      <c r="B56" s="184">
+        <f>SUM(F:Q) — Total of all 12 months. This is the base for ABC classification.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="182" t="inlineStr">
+        <is>
+          <t>Col S (Mean Monthly)</t>
+        </is>
+      </c>
+      <c r="B57" s="183">
+        <f>R/12 — Average demand per month. Used as denominator in CV calculation.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="182" t="inlineStr">
+        <is>
+          <t>Col T (Std Dev)</t>
+        </is>
+      </c>
+      <c r="B58" s="184">
+        <f>STDEV(F:Q) — Excel's standard deviation of 12 monthly values. Measures how much demand FLUCTUATES. High Std Dev = unpredictable part.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="182" t="inlineStr">
+        <is>
+          <t>Col U (CV)</t>
+        </is>
+      </c>
+      <c r="B59" s="183">
+        <f>Std Dev / Mean Monthly. Dimensionless ratio. CV &lt; 0.10 = X (stable). CV 0.10–0.30 = Y (variable). CV &gt; 0.30 = Z (intermittent/sporadic).</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="182" t="inlineStr">
+        <is>
+          <t>Col V (ABC)</t>
+        </is>
+      </c>
+      <c r="B60" s="184">
+        <f>IF(Cumul%&lt;=0.7,"A",IF(Cumul%&lt;=0.9,"B","C")) — A = top 70% of annual value. B = next 20%. C = bottom 10%. Sort by Annual Value DESC to see true cumulative.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="182" t="inlineStr">
+        <is>
+          <t>Col W (XYZ)</t>
+        </is>
+      </c>
+      <c r="B61" s="183">
+        <f>IF(CV&lt;0.1,"X",IF(CV&lt;0.3,"Y","Z")) — X = steady demand. Y = moderate variation. Z = intermittent (sporadic, unpredictable).</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="182" t="inlineStr">
+        <is>
+          <t>Col X (Combined)</t>
+        </is>
+      </c>
+      <c r="B62" s="184">
+        <f>ABC &amp; XYZ — e.g. AZ means high-value part with sporadic demand. This combination determines the REPLENISHMENT STRATEGY.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="182" t="inlineStr">
+        <is>
+          <t>Col Y (Annual Value)</t>
+        </is>
+      </c>
+      <c r="B63" s="183">
+        <f>Unit Cost × Annual Demand. The higher this is, the more important the part is to manage tightly.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="182" t="inlineStr">
+        <is>
+          <t>Col Z (Cumul Value %)</t>
+        </is>
+      </c>
+      <c r="B64" s="184">
+        <f>This part's value / Total portfolio value. Used to draw the ABC Pareto boundary. </f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A54:AB54"/>
+    <mergeCell ref="B56:AB56"/>
+    <mergeCell ref="B58:AB58"/>
+    <mergeCell ref="B62:AB62"/>
+    <mergeCell ref="B64:AB64"/>
+    <mergeCell ref="B55:AB55"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="B59:AB59"/>
+    <mergeCell ref="B60:AB60"/>
+    <mergeCell ref="B63:AB63"/>
+    <mergeCell ref="B61:AB61"/>
+    <mergeCell ref="B57:AB57"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="50" customHeight="1">
+      <c r="A1" s="185" t="inlineStr">
+        <is>
+          <t>FUSO MEA Demand Planning — Calculation Explainer  |  Read This Sheet to Understand Every Formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="186" t="inlineStr">
+        <is>
+          <t>Each row below explains ONE metric: what it is, the exact formula, a plain-English explanation, a worked numerical example, and what it means for FUSO MEA.  Use this as your reference — you do not need to memorise anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  SECTION A — ABC ANALYSIS: Classifying Parts by Annual Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="188" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="188" t="inlineStr">
+        <is>
+          <t>METRIC</t>
+        </is>
+      </c>
+      <c r="C4" s="189" t="inlineStr">
+        <is>
+          <t>EXACT FORMULA</t>
+        </is>
+      </c>
+      <c r="D4" s="190" t="inlineStr">
+        <is>
+          <t>PLAIN ENGLISH — WHAT IT MEANS</t>
+        </is>
+      </c>
+      <c r="E4" s="191" t="inlineStr">
+        <is>
+          <t>WORKED EXAMPLE (Real FUSO Part)</t>
+        </is>
+      </c>
+      <c r="F4" s="192" t="inlineStr">
+        <is>
+          <t>FUSO MEA RESULT / SO WHAT?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="193" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B5" s="194" t="inlineStr">
+        <is>
+          <t>Annual Value
+(AED)</t>
+        </is>
+      </c>
+      <c r="C5" s="195">
+        <f> Unit Cost × Annual Demand
+=E3*F3</f>
+        <v/>
+      </c>
+      <c r="D5" s="196" t="inlineStr">
+        <is>
+          <t>Annual Value = what we SPEND on this part per year.
+A part costing AED 420 each that we use 600 units/year costs AED 252,000/year.
+This is more important to manage than a AED 45 filter used 1,800 times = AED 81,000/year — even though the filter has MORE units.</t>
+        </is>
+      </c>
+      <c r="E5" s="197" t="inlineStr">
+        <is>
+          <t>FUSO-CLT-006 Clutch Disc:
+Cost = AED 420
+Annual Demand = 600 units
+Annual Value = 420 × 600
+= AED 252,000 ← A-Class</t>
+        </is>
+      </c>
+      <c r="F5" s="198" t="inlineStr">
+        <is>
+          <t>All 50 SKUs ranked by Annual Value DESC. Top 21 SKUs = 69% of AED 38M portfolio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="193" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B6" s="194" t="inlineStr">
+        <is>
+          <t>Cumulative
+Value %</t>
+        </is>
+      </c>
+      <c r="C6" s="195">
+        <f> This SKU's Annual Value ÷ SUM of all SKUs' Annual Values
+=G3/SUM($G$3:$G$52)
+Then SORT the list by Annual Value DESC before computing cumul.</f>
+        <v/>
+      </c>
+      <c r="D6" s="196" t="inlineStr">
+        <is>
+          <t>After sorting all 50 parts from most expensive to least, add up their values one by one.
+The cumulative % tells you: 'At this point in the list, what % of total spend have we covered?'
+When you hit 70%: everything above = A-Class.
+When you hit 90%: everything between 70-90% = B-Class.
+Everything after = C-Class.</t>
+        </is>
+      </c>
+      <c r="E6" s="197" t="inlineStr">
+        <is>
+          <t>Sorted top 3:
+1. Battery Module AED 108K → cumul 2.3%
+2. eCanter Charger AED 76K → cumul 3.9%
+3. Turbocharger AED 182K → cumul 7.7%
+...continues until cumul hits 70% → that boundary = A/B line</t>
+        </is>
+      </c>
+      <c r="F6" s="198" t="inlineStr">
+        <is>
+          <t>21 parts = A-Class (69.3% of spend)
+13 parts = B-Class (next 19.7%)
+16 parts = C-Class (bottom 11%)
+Pareto principle confirmed: 42% of SKUs drive 69% of spend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="193" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B7" s="194" t="inlineStr">
+        <is>
+          <t>ABC Class
+Assignment</t>
+        </is>
+      </c>
+      <c r="C7" s="195">
+        <f>IF(CumulValue%&lt;=0.7,"A",
+  IF(CumulValue%&lt;=0.9,"B","C"))
+=IF(H3&lt;=0.7,"A",IF(H3&lt;=0.9,"B","C"))</f>
+        <v/>
+      </c>
+      <c r="D7" s="196" t="inlineStr">
+        <is>
+          <t>Simple three-tier assignment:
+A = Cumulative value ≤ 70% → TOP PRIORITY. Never stockout.
+B = Cumulative value ≤ 90% → IMPORTANT. Monitor regularly.
+C = Cumulative value &gt; 90% → LOW PRIORITY. Minimal effort.
+The thresholds 70/90 are APICS industry standard for automotive spare parts. Tighter than retail FMCG (80/95) because spare part values are more skewed.</t>
+        </is>
+      </c>
+      <c r="E7" s="197" t="inlineStr">
+        <is>
+          <t>If sorted cumul% at row 21 = 69.3% → A
+If sorted cumul% at row 34 = 89.0% → B
+If sorted cumul% at row 50 = 100% → C
+FUSO-BRK-001 Brake Pad: cumul = 56% → A
+FUSO-LAM-046 Lambda Sensor: cumul = 82% → B
+FUSO-VLV-029 Valve Gasket: cumul = 97% → C</t>
+        </is>
+      </c>
+      <c r="F7" s="198" t="inlineStr">
+        <is>
+          <t>A-parts get:
+• Z-score = 2.05 (99% service level)
+• Continuous review (daily monitoring)
+• Strict safety stock formula
+C-parts get:
+• Z-score = 1.28 (90% SL)
+• Annual review only</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  SECTION B — XYZ ANALYSIS: Classifying Parts by Demand Predictability</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="188" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="188" t="inlineStr">
+        <is>
+          <t>METRIC</t>
+        </is>
+      </c>
+      <c r="C9" s="189" t="inlineStr">
+        <is>
+          <t>EXACT FORMULA</t>
+        </is>
+      </c>
+      <c r="D9" s="190" t="inlineStr">
+        <is>
+          <t>PLAIN ENGLISH — WHAT IT MEANS</t>
+        </is>
+      </c>
+      <c r="E9" s="191" t="inlineStr">
+        <is>
+          <t>WORKED EXAMPLE (Real FUSO Part)</t>
+        </is>
+      </c>
+      <c r="F9" s="192" t="inlineStr">
+        <is>
+          <t>FUSO MEA RESULT / SO WHAT?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="193" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B10" s="194" t="inlineStr">
+        <is>
+          <t>Standard Deviation
+of Monthly Demand
+(Demand Std Dev)</t>
+        </is>
+      </c>
+      <c r="C10" s="195">
+        <f> STDEV of 12 monthly demand values
+=STDEV(Apr25:Mar26)
+= STDEV(F3:Q3)
+Standard Excel formula. Measures how much monthly demand deviates from the average.</f>
+        <v/>
+      </c>
+      <c r="D10" s="196" t="inlineStr">
+        <is>
+          <t>Standard Deviation measures SPREAD of demand.
+If monthly demand is: 48, 52, 47, 51, 49, 53
+→ Mean = 50, Std Dev = 2.3 (very stable)
+If monthly demand is: 0, 0, 120, 0, 0, 60
+→ Mean = 30, Std Dev = 46 (highly erratic)
+Same MEAN, completely different predictability.
+Std Dev alone doesn't compare across parts — that's why we use CV.</t>
+        </is>
+      </c>
+      <c r="E10" s="197" t="inlineStr">
+        <is>
+          <t>FUSO-CLT-006 Clutch Disc:
+Monthly: 45,52,48,55,42,49,51,47,53,46,50,62
+Mean = 50  |  Std Dev = STDEV(...) = 5.3
+FUSO-TRB-021 Turbocharger:
+Monthly: 0,0,0,48,0,0,0,0,0,0,0,0
+Mean = 4  |  Std Dev = STDEV(...) = 13.9</t>
+        </is>
+      </c>
+      <c r="F10" s="198" t="inlineStr">
+        <is>
+          <t>Clutch Disc: Std Dev = 5.3 (predictable)
+Turbocharger: Std Dev = 13.9 (but mean only 4!)
+We CANNOT compare these raw numbers.
+We need CV to normalise them → see B2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="193" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B11" s="194" t="inlineStr">
+        <is>
+          <t>Coefficient of
+Variation (CV)
+The key ratio for
+XYZ classification</t>
+        </is>
+      </c>
+      <c r="C11" s="195">
+        <f> Std Dev ÷ Mean Monthly Demand
+=IF(MeanMonthly=0, 9999, StdDev/MeanMonthly)
+=IF(K3=0, 9999, J3/K3)
+IF(K3=0,...) protects against ÷ zero
+when a part has no demand at all.</f>
+        <v/>
+      </c>
+      <c r="D11" s="196" t="inlineStr">
+        <is>
+          <t>CV = How variable is demand RELATIVE TO its own average?
+CV = 0.05 → demand barely moves. Very predictable.
+CV = 0.50 → demand swings ±50% of the mean. Unpredictable.
+CV = 2.0  → demand is wildly erratic (mostly zeros).
+CV is dimensionless — it removes the unit problem. Now we can fairly compare a AED 45 oil filter (high volume) with a AED 18,000 battery module (very low volume).</t>
+        </is>
+      </c>
+      <c r="E11" s="197" t="inlineStr">
+        <is>
+          <t>Oil Filter (FUSO-OIL-002):
+Mean = 150/month  |  Std Dev = 8
+CV = 8/150 = 0.053 → X (Stable)
+Shock Absorber (FUSO-SHK-012):
+Mean = 30/month  |  Std Dev = 22
+CV = 22/30 = 0.733 → Z (Intermittent)
+Turbocharger (FUSO-TRB-021):
+Mean = 4/month  |  Std Dev = 14
+CV = 14/4 = 3.5 → Z (Very sparse)</t>
+        </is>
+      </c>
+      <c r="F11" s="198" t="inlineStr">
+        <is>
+          <t>FUSO MEA result:
+X-class: 0 SKUs (0%) — no perfectly stable parts
+Y-class: 15 SKUs (30%) — moderate variability
+Z-class: 35 SKUs (70%) — intermittent!
+70% intermittent = WHY SAP APO fails at 70%
+SAP APO assumes stable demand. Z-parts need SBA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="193" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B12" s="194" t="inlineStr">
+        <is>
+          <t>XYZ Class
+Assignment
+Boundaries:
+&lt; 0.10 = X
+0.10–0.30 = Y
+&gt; 0.30 = Z</t>
+        </is>
+      </c>
+      <c r="C12" s="195">
+        <f>IF(CV&lt;0.1,"X",IF(CV&lt;0.3,"Y","Z"))
+=IF(L3&lt;0.1,"X",IF(L3&lt;0.3,"Y","Z"))
+Thresholds from Scholz-Reiter et al.
+(standard supply chain literature)</f>
+        <v/>
+      </c>
+      <c r="D12" s="196" t="inlineStr">
+        <is>
+          <t>X = CV &lt; 0.10: Demand is very regular. Basic forecasting works. Textbook min-max or Kanban.
+Y = 0.10 ≤ CV &lt; 0.30: Demand has some trend or seasonality. Exponential smoothing handles this. Review more frequently.
+Z = CV ≥ 0.30: Demand is sporadic or intermittent. Standard forecasting will systematically OVER-forecast. Must use Croston's method or SBA (Syntetos-Boylan Approximation).</t>
+        </is>
+      </c>
+      <c r="E12" s="197" t="inlineStr">
+        <is>
+          <t>CV = 0.053 (Oil Filter) → 0.053 &lt; 0.10 → X
+CV = 0.196 (Clutch Disc) → 0.10-0.30 → Y
+CV = 0.733 (Shock Absorber) → &gt;0.30 → Z
+Why does CV=0.3 divide Y from Z?
+At CV=0.30 a moving average starts producing
+forecasts with &gt;30% average error — no longer
+reliable enough for safety stock decisions.</t>
+        </is>
+      </c>
+      <c r="F12" s="198" t="inlineStr">
+        <is>
+          <t>35 out of 50 FUSO parts are Z-class.
+This is EXPECTED for spare parts.
+Turbochargers, injectors, ECUs don't fail
+on a schedule — they fail randomly.
+This is why the role exists:
+to apply the RIGHT method per class,
+not one method for all 50 parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  SECTION C — COMBINED ABC-XYZ CLASS &amp; REPLENISHMENT STRATEGY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="188" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B14" s="188" t="inlineStr">
+        <is>
+          <t>METRIC</t>
+        </is>
+      </c>
+      <c r="C14" s="189" t="inlineStr">
+        <is>
+          <t>EXACT FORMULA</t>
+        </is>
+      </c>
+      <c r="D14" s="190" t="inlineStr">
+        <is>
+          <t>PLAIN ENGLISH — WHAT IT MEANS</t>
+        </is>
+      </c>
+      <c r="E14" s="191" t="inlineStr">
+        <is>
+          <t>WORKED EXAMPLE (Real FUSO Part)</t>
+        </is>
+      </c>
+      <c r="F14" s="192" t="inlineStr">
+        <is>
+          <t>FUSO MEA RESULT / SO WHAT?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="193" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B15" s="194" t="inlineStr">
+        <is>
+          <t>Combined
+ABC-XYZ Class
+e.g. AZ, BY, CZ</t>
+        </is>
+      </c>
+      <c r="C15" s="195">
+        <f> ABC Class &amp; XYZ Class
+=IF(ABC="A","A","...")
+  &amp; IF(XYZ="Z","Z","...")
+Simply concatenates the two letters.
+Result: AX, AY, AZ, BX, BY, BZ, CX, CY, CZ</f>
+        <v/>
+      </c>
+      <c r="D15" s="196" t="inlineStr">
+        <is>
+          <t>The 9-cell matrix is the MASTER DECISION TOOL.
+It answers TWO questions at once:
+1. How valuable is this part? (ABC)
+2. How predictable is demand? (XYZ)
+The combination tells you EXACTLY what to do:
+how to forecast, how much safety stock to hold,
+how often to review, and what happens if you get it wrong.</t>
+        </is>
+      </c>
+      <c r="E15" s="197" t="inlineStr">
+        <is>
+          <t>FUSO-WPM-007 Water Pump:
+Annual Value = AED 182,400 → ABC = A
+CV = 0.175 → XYZ = Y
+Combined = AY
+→ (R,S) Periodic Review
+FUSO-TIM-028 Timing Chain:
+Annual Value = AED 33,600 → ABC = C
+CV = 1.44 → XYZ = Z
+Combined = CZ
+→ SMOB Candidate. Do not replenish.</t>
+        </is>
+      </c>
+      <c r="F15" s="198" t="inlineStr">
+        <is>
+          <t>FUSO MEA breakdown:
+AY = 5 parts (high value, periodic review)
+AZ = 16 parts (high value, SBA + buffer)
+BY = 6 parts (medium, exp smoothing)
+BZ = 7 parts (medium, SBA)
+CY = 4 parts (low, annual review)
+CZ = 12 parts (SMOB candidates — 24% of SKUs!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="193" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B16" s="194" t="inlineStr">
+        <is>
+          <t>Replenishment
+Strategy
+(VLOOKUP)</t>
+        </is>
+      </c>
+      <c r="C16" s="195">
+        <f>IFERROR(
+  VLOOKUP(CombinedClass,
+    StrategyTable, 2, FALSE),
+  'Manual Review')
+Looks up the 9-row strategy table
+and returns the matching policy.</f>
+        <v/>
+      </c>
+      <c r="D16" s="196" t="inlineStr">
+        <is>
+          <t>VLOOKUP finds the combined class (e.g. 'AZ') in a lookup
+table and returns the recommended inventory policy.
+IFERROR catches any lookup failures (e.g. data entry errors)
+and returns 'Manual Review' instead of showing an error.
+The strategy table is fixed — once built, every new SKU
+automatically gets the right strategy just by having
+its ABC and XYZ classified correctly.</t>
+        </is>
+      </c>
+      <c r="E16" s="197" t="inlineStr">
+        <is>
+          <t>AX → Min-Max / Continuous Review
+(check daily, order when below minimum)
+AZ → Demand Sensing + Buffer Stock
+(hold extra buffer, use SBA forecast)
+CZ → SMOB Candidate / Order-on-Demand
+(do NOT replenish proactively;
+ only order when a specific customer
+ order arrives)</t>
+        </is>
+      </c>
+      <c r="F16" s="198" t="inlineStr">
+        <is>
+          <t>The strategy table removes HUMAN DISCRETION
+from routine inventory decisions.
+No one needs to decide whether to stock
+a part — the combined class decides it.
+This is how demand planners scale to
+manage 100,000+ SKUs in large portfolios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  SECTION D — SMOB FLAG &amp; DISPOSITION: Managing Slow-Moving Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="188" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B18" s="188" t="inlineStr">
+        <is>
+          <t>METRIC</t>
+        </is>
+      </c>
+      <c r="C18" s="189" t="inlineStr">
+        <is>
+          <t>EXACT FORMULA</t>
+        </is>
+      </c>
+      <c r="D18" s="190" t="inlineStr">
+        <is>
+          <t>PLAIN ENGLISH — WHAT IT MEANS</t>
+        </is>
+      </c>
+      <c r="E18" s="191" t="inlineStr">
+        <is>
+          <t>WORKED EXAMPLE (Real FUSO Part)</t>
+        </is>
+      </c>
+      <c r="F18" s="192" t="inlineStr">
+        <is>
+          <t>FUSO MEA RESULT / SO WHAT?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="193" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B19" s="194" t="inlineStr">
+        <is>
+          <t>SMOB Flag
+Slow Moving
+&amp; OBsolete</t>
+        </is>
+      </c>
+      <c r="C19" s="202">
+        <f>IF(AND(XYZ="Z", ABC="C"),
+  "SMOB RISK", "OK")
+=IF(AND(M3="Z",I3="C"),
+  "SMOB RISK","OK")</f>
+        <v/>
+      </c>
+      <c r="D19" s="196" t="inlineStr">
+        <is>
+          <t>SMOB = Slow Moving and OBsolete stock.
+A part is flagged SMOB RISK when BOTH are true:
+• XYZ = Z (demand is sporadic — barely moves)
+• ABC = C (low annual value — not worth holding)
+AND() requires BOTH conditions — not just one.
+A high-value sporadic part (AZ) is NOT flagged — it needs
+a buffer stock, not liquidation.</t>
+        </is>
+      </c>
+      <c r="E19" s="203" t="inlineStr">
+        <is>
+          <t>FUSO-TIM-028 Timing Chain Kit:
+XYZ = Z (CV = 1.44, barely moves)
+ABC = C (AED 33,600/yr = bottom 10%)
+AND(Z, C) = TRUE → SMOB RISK
+FUSO-TRB-021 Turbocharger:
+XYZ = Z (sporadic demand)
+ABC = A (AED 182,400/yr = top value)
+AND(Z, C) = FALSE → OK (manage with buffer)</t>
+        </is>
+      </c>
+      <c r="F19" s="204" t="inlineStr">
+        <is>
+          <t>10 parts flagged SMOB RISK.
+Together = 18% of AED 38M portfolio value.
+= AED 6.84M sitting idle in Jafza warehouse.
+Industry benchmark: &lt;5% SMOB.
+Target: reduce to &lt;5% within 36 months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="70" customHeight="1">
+      <c r="A20" s="193" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B20" s="194" t="inlineStr">
+        <is>
+          <t>Months Zero
+Demand
+Col Q in
+ABC_XYZ sheet</t>
+        </is>
+      </c>
+      <c r="C20" s="195" t="inlineStr">
+        <is>
+          <t>Manually populated from
+SAP MB52 / MMBE stock
+consumption report.
+Counts how many of the
+last 12 months had zero
+goods issue recorded.</t>
+        </is>
+      </c>
+      <c r="D20" s="196" t="inlineStr">
+        <is>
+          <t>Zero demand months = months where no stock was consumed.
+⚠ IMPORTANT NUANCE:
+Zero demand can mean TWO things:
+1. TRUE ZERO: Part in stock, no customer asked for it.
+2. HIDDEN STOCKOUT: Part was out of stock, so no demand
+   could be recorded even if customers needed it.
+You must cross-check SAP stock levels. If stock = 0 AND
+demand = 0, it may be a stockout — NOT a slow mover.
+This distinction is critical before flagging SMOB.</t>
+        </is>
+      </c>
+      <c r="E20" s="197" t="inlineStr">
+        <is>
+          <t>FUSO-TIM-028 Timing Chain:
+SAP shows: 18 units in stock, 0 goods issues
+in last 18 months. Stock was available but
+no one ordered. → TRUE slow mover.
+vs.
+FUSO-TRB-021 Turbocharger:
+SAP shows: 0 stock, 0 demand in 2 months.
+→ Possible stockout. Investigate before flagging.</t>
+        </is>
+      </c>
+      <c r="F20" s="198" t="inlineStr">
+        <is>
+          <t>18 months no movement (Timing Chain) =
+holding cost = 18 × 2.5% × AED 50,400
+= AED 22,680 in storage costs already paid.
+Every month delayed costs more.
+Act at 6 months (LIQUIDATE threshold).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="70" customHeight="1">
+      <c r="A21" s="193" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B21" s="194" t="inlineStr">
+        <is>
+          <t>Disposition
+Decision
+LIQUIDATE /
+REVIEW /
+ACTIVE</t>
+        </is>
+      </c>
+      <c r="C21" s="202">
+        <f>IF(AND(SMOBFlag="SMOB RISK",
+        MonthsNoMove&gt;6),
+  "LIQUIDATE",
+  IF(MonthsNoMove&gt;3,
+    "REVIEW", "ACTIVE"))
+=IF(AND(P3="SMOB RISK",Q3&gt;6),
+  "LIQUIDATE",IF(Q3&gt;3,
+  "REVIEW","ACTIVE"))</f>
+        <v/>
+      </c>
+      <c r="D21" s="196" t="inlineStr">
+        <is>
+          <t>LIQUIDATE: Both conditions are true — it's SMOB risk AND
+has been idle more than 6 months. At 6+ months of inactivity,
+holding cost exceeds likely recovery value at normal price.
+Take action now: Bundle / Rotate / Write-off.
+REVIEW: Any part (any class) idle 3-6 months. Early warning.
+Is it seasonal? Discontinued? Supply problem? Investigate.
+ACTIVE: Less than 3 months idle. Normal Z-class behaviour.
+Continue monitoring. No action yet.</t>
+        </is>
+      </c>
+      <c r="E21" s="197" t="inlineStr">
+        <is>
+          <t>6-month threshold logic:
+Dubai climate-controlled storage ≈ 2.5%/month holding cost
+At 6 months = 15% of part value paid in storage.
+At 12 months = 30% paid in storage.
+FUSO-TIM-028: 18 months × 2.5% × AED 50,400
+= AED 22,680 already spent storing it.
+Scrap/write-off is now cheaper than holding.</t>
+        </is>
+      </c>
+      <c r="F21" s="204" t="inlineStr">
+        <is>
+          <t>3-step FUSO SMOB Plan:
+BUNDLE (3 parts): Package with fast-moving
+service kits at 20% discount to clear stock.
+ROTATE (4 parts): Offer to 58 MEA distributors.
+One market's slow-mover = another's need.
+SCRAP (3 parts): Discontinued model, no fleet
+remaining. Write-off cost to P&amp;L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  SECTION E — SAFETY STOCK &amp; REORDER POINT: How Much Buffer to Hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="188" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B23" s="188" t="inlineStr">
+        <is>
+          <t>METRIC</t>
+        </is>
+      </c>
+      <c r="C23" s="189" t="inlineStr">
+        <is>
+          <t>EXACT FORMULA</t>
+        </is>
+      </c>
+      <c r="D23" s="190" t="inlineStr">
+        <is>
+          <t>PLAIN ENGLISH — WHAT IT MEANS</t>
+        </is>
+      </c>
+      <c r="E23" s="191" t="inlineStr">
+        <is>
+          <t>WORKED EXAMPLE (Real FUSO Part)</t>
+        </is>
+      </c>
+      <c r="F23" s="192" t="inlineStr">
+        <is>
+          <t>FUSO MEA RESULT / SO WHAT?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="70" customHeight="1">
+      <c r="A24" s="193" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B24" s="194" t="inlineStr">
+        <is>
+          <t>Safety Stock
+(Standard Formula)
+Block A:
+For Japan &amp;
+Chennai supply</t>
+        </is>
+      </c>
+      <c r="C24" s="195" t="inlineStr">
+        <is>
+          <t>SS = Z × σ_demand × √(LT + R)
+where:
+Z = service level Z-score
+σ_demand = daily demand std dev
+LT = lead time (days)
+R = review period (days)
+σ_demand = monthly std dev ÷ 30</t>
+        </is>
+      </c>
+      <c r="D24" s="196" t="inlineStr">
+        <is>
+          <t>Safety stock is the BUFFER held ABOVE average demand
+during lead time. It protects against two risks:
+1. Demand being higher than forecast
+2. Supplier delivering late
+Z × σ_demand sets the width of the buffer.
+√(LT+R) scales it over the full exposure period.
+Larger Z = more safety stock = higher service level
+but more capital tied up.</t>
+        </is>
+      </c>
+      <c r="E24" s="197" t="inlineStr">
+        <is>
+          <t>FUSO-CLT-006 Clutch Disc (A-class, Japan):
+Z = 2.05 (A-class, 99% service level)
+σ_demand_monthly = 8 units
+σ_demand_daily = 8/30 = 0.267 units/day
+LT = 45 days (Japan)
+R = 30 days (monthly review)
+SS = 2.05 × 0.267 × √(45+30)
+   = 2.05 × 0.267 × 8.66
+   = 4.7 units ≈ 5 units</t>
+        </is>
+      </c>
+      <c r="F24" s="198" t="inlineStr">
+        <is>
+          <t>Japan supply: LT variability σ_LT = 2 days
+→ Standard formula is sufficient
+Chennai supply: σ_LT = 3 days
+→ Standard formula also acceptable
+Germany/GPC: σ_LT = 10 days
+→ Standard formula UNDERSTATES SS
+→ MUST use Enhanced formula (E2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="70" customHeight="1">
+      <c r="A25" s="193" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B25" s="194" t="inlineStr">
+        <is>
+          <t>Safety Stock
+(Enhanced Formula)
+Block B:
+For GPC Halberstadt
+(high LT variability)</t>
+        </is>
+      </c>
+      <c r="C25" s="195" t="inlineStr">
+        <is>
+          <t>SS = Z × √(LT×σ_d² + D̄²×σ_LT²)
+Additional term: D̄² × σ_LT²
+= (Avg daily demand)² ×
+  (Lead time std dev)²
+This term captures EXTRA RISK
+from unpredictable delivery dates.</t>
+        </is>
+      </c>
+      <c r="D25" s="196" t="inlineStr">
+        <is>
+          <t>The enhanced formula adds a second source of uncertainty:
+LEAD TIME VARIABILITY.
+If a shipment might arrive anywhere from day 20 to day 40,
+you need more safety stock to cover the worst case.
+The extra term D̄² × σ_LT² quantifies this:
+If your avg daily demand is 1.64 units AND σ_LT = 10 days,
+you could receive 1.64 × 10 = 16.4 fewer units in the worst
+case of a 10-day delay. The formula captures this risk.</t>
+        </is>
+      </c>
+      <c r="E25" s="197" t="inlineStr">
+        <is>
+          <t>FUSO-BRK-001 Brake Pad (GPC supply):
+Z = 2.05 (A-class)
+LT = 30 days, σ_LT = 10 days (ramp-up!)
+D̄ = 3.29 units/day
+σ_d = 0.4 units/day
+SS = 2.05 × √(30×0.16 + 3.29²×100)
+   = 2.05 × √(4.8 + 1083)
+   = 2.05 × 32.9 = 67 units
+vs. Japan formula = 28 units only!</t>
+        </is>
+      </c>
+      <c r="F25" s="198" t="inlineStr">
+        <is>
+          <t>KEY INSIGHT:
+GPC lead time 30d &lt; Japan 45d
+BUT σ_LT=10 vs σ_LT=2
+Result: SS DOUBLES for GPC vs Japan
+despite shorter average lead time.
+Bridge stock investment = AED 1.07M
+for top 20 high-runner parts.
+Must be pre-approved BEFORE
+first GPC shipment arrives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="70" customHeight="1">
+      <c r="A26" s="193" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B26" s="194" t="inlineStr">
+        <is>
+          <t>Reorder Point
+(ROP)
+When to place
+the next order</t>
+        </is>
+      </c>
+      <c r="C26" s="195" t="inlineStr">
+        <is>
+          <t>ROP = (Average Daily Demand × LT) + SS
+= D̄ × LT + SS
+When stock falls to this level,
+place your replenishment order NOW
+so it arrives before you run out.</t>
+        </is>
+      </c>
+      <c r="D26" s="196" t="inlineStr">
+        <is>
+          <t>ROP is the TRIGGER POINT for ordering.
+D̄ × LT = the stock you'll consume WHILE
+waiting for the supplier to deliver.
+SS = buffer for when demand is higher or
+supplier is later than expected.
+ROP = expected consumption during lead time
+      + safety buffer = ORDER NOW threshold.</t>
+        </is>
+      </c>
+      <c r="E26" s="197" t="inlineStr">
+        <is>
+          <t>FUSO-CLT-006 Clutch Disc:
+D̄ = 600/365 = 1.64 units/day
+LT = 45 days (Japan)
+SS = 5 units (calculated above)
+ROP = (1.64 × 45) + 5
+    = 73.8 + 5
+    = 79 units
+When Jafza stock falls below 79 units,
+PLACE ORDER to Japan immediately.</t>
+        </is>
+      </c>
+      <c r="F26" s="198" t="inlineStr">
+        <is>
+          <t>ROP tells the warehouse team:
+'When stock hits this number, order more.'
+No calculation needed at order time —
+the ROP is pre-computed and set in SAP
+as the re-order trigger.
+Demand planner's job: recalculate ROP
+monthly (S&amp;OP cycle) as demand patterns
+and lead times change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  SECTION F — SBA FORECASTING: Why We Don't Use Standard Methods for Z-Class Parts</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="188" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B28" s="188" t="inlineStr">
+        <is>
+          <t>METRIC</t>
+        </is>
+      </c>
+      <c r="C28" s="189" t="inlineStr">
+        <is>
+          <t>EXACT FORMULA</t>
+        </is>
+      </c>
+      <c r="D28" s="190" t="inlineStr">
+        <is>
+          <t>PLAIN ENGLISH — WHAT IT MEANS</t>
+        </is>
+      </c>
+      <c r="E28" s="191" t="inlineStr">
+        <is>
+          <t>WORKED EXAMPLE (Real FUSO Part)</t>
+        </is>
+      </c>
+      <c r="F28" s="192" t="inlineStr">
+        <is>
+          <t>FUSO MEA RESULT / SO WHAT?</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="70" customHeight="1">
+      <c r="A29" s="193" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B29" s="194" t="inlineStr">
+        <is>
+          <t>Why SAP APO
+Fails on
+Z-Class Parts</t>
+        </is>
+      </c>
+      <c r="C29" s="207" t="inlineStr">
+        <is>
+          <t>Standard Moving Average:
+Forecast = AVG(last N months)
+Applied to: 0,0,0,40,0,0
+Forecast = 40/6 = 6.7/month
+Reality: demand occurs in bursts,
+not steadily at 6.7/month.
+This forecast is ALWAYS wrong.</t>
+        </is>
+      </c>
+      <c r="D29" s="196" t="inlineStr">
+        <is>
+          <t>Moving averages assume demand occurs EVERY period.
+For Z-class parts, demand arrives in bursts
+separated by long zero-demand gaps.
+The average of the zeros and the burst equals a
+low continuous rate — which never actually happens.
+The part is EITHER in demand (burst) OR not (zero).
+SAP APO's standard method was designed for FMCG.
+It is the wrong tool for spare parts.</t>
+        </is>
+      </c>
+      <c r="E29" s="208" t="inlineStr">
+        <is>
+          <t>Water Pump demand: 0, 0, 0, 40, 0, 0
+SAP APO forecast: 40/6 = 6.7 units/month
+→ Orders 6.7 units every month
+→ Builds up unwanted stock for 5 months
+→ Then under-stocks when burst hits
+SBA forecast:
+Demand size: 40 units (when it occurs)
+Demand interval: every 4 months avg
+SBA rate: 40/4 = 10 units/event (correct!)</t>
+        </is>
+      </c>
+      <c r="F29" s="198" t="inlineStr">
+        <is>
+          <t>SAP APO baseline accuracy: 70%
+Root cause: 35 Z-class parts (70% of SKUs)
+being forecast with a tool designed
+for steady demand.
+SBA applied to Z-class parts alone
+lifts accuracy to ~78%.
+Full implementation target: 85% by 2028.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="70" customHeight="1">
+      <c r="A30" s="193" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B30" s="194" t="inlineStr">
+        <is>
+          <t>SBA Method
+(Syntetos-Boylan
+Approximation)
+The correct
+method for
+Z-class parts</t>
+        </is>
+      </c>
+      <c r="C30" s="195" t="inlineStr">
+        <is>
+          <t>F_SBA = (1 - α/2) × (Ẑ ÷ p̂)
+where:
+Ẑ = smoothed demand size
+    (how much when demand hits)
+p̂ = smoothed demand interval
+    (how many periods between events)
+α = smoothing constant (0.1)
+(1-α/2) = bias correction factor</t>
+        </is>
+      </c>
+      <c r="D30" s="196" t="inlineStr">
+        <is>
+          <t>SBA separates ONE question into TWO:
+1. WHEN will demand happen? (interval p̂)
+2. HOW MUCH when it does? (size Ẑ)
+Croston (1972) invented this split but had an upward bias.
+Syntetos &amp; Boylan (2001) proved Croston over-forecasts
+by α/2. The correction (1-α/2) removes this bias.
+With α=0.10: correction = (1 - 0.05) = 0.95
+= 5% downward adjustment to Croston's estimate.</t>
+        </is>
+      </c>
+      <c r="E30" s="197" t="inlineStr">
+        <is>
+          <t>Water Pump: demand 0,0,0,40,0,0
+Demand events: 1 event of 40 units
+Ẑ (smoothed size) = 40
+p̂ (smoothed interval) = 4 months
+α = 0.10
+F_SBA = (1 - 0.10/2) × (40/4)
+      = 0.95 × 10
+      = 9.5 units per event
+vs SAP APO: 6.7 units/month (wrong)</t>
+        </is>
+      </c>
+      <c r="F30" s="198" t="inlineStr">
+        <is>
+          <t>Why α = 0.10 for FUSO spare parts?
+Low α = slow to respond to new data.
+This is correct for spare parts because:
+• One emergency VOR order of 40 units should
+  NOT inflate the long-run forecast permanently.
+• Spare part demand patterns are structural,
+  not trend-driven.
+High α (0.3-0.5) is for FMCG with fast
+trend response. Wrong for spare parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  SECTION G — SERVICE LEVEL &amp; Z-SCORE: How Confident Do We Want to Be?</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="188" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B32" s="188" t="inlineStr">
+        <is>
+          <t>METRIC</t>
+        </is>
+      </c>
+      <c r="C32" s="189" t="inlineStr">
+        <is>
+          <t>EXACT FORMULA</t>
+        </is>
+      </c>
+      <c r="D32" s="190" t="inlineStr">
+        <is>
+          <t>PLAIN ENGLISH — WHAT IT MEANS</t>
+        </is>
+      </c>
+      <c r="E32" s="191" t="inlineStr">
+        <is>
+          <t>WORKED EXAMPLE (Real FUSO Part)</t>
+        </is>
+      </c>
+      <c r="F32" s="192" t="inlineStr">
+        <is>
+          <t>FUSO MEA RESULT / SO WHAT?</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="70" customHeight="1">
+      <c r="A33" s="193" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B33" s="194" t="inlineStr">
+        <is>
+          <t>Service Level
+&amp; Z-Score
+NORM.S.INV()
+Why we hold
+different SS
+for A vs C parts</t>
+        </is>
+      </c>
+      <c r="C33" s="195" t="inlineStr">
+        <is>
+          <t>Z = NORM.S.INV(service_level)
+NORM.S.INV(0.95) = 1.645
+NORM.S.INV(0.99) = 2.326
+NORM.S.INV(0.90) = 1.282
+FUSO tiered approach:
+A-class: Z=2.05 (97.9% SL)
+B-class: Z=1.65 (95.0% SL)
+C-class: Z=1.28 (90.0% SL)</t>
+        </is>
+      </c>
+      <c r="D33" s="196" t="inlineStr">
+        <is>
+          <t>Service Level = probability of NOT running out of stock
+in any given replenishment cycle.
+95% SL = in 95 out of 100 replenishment cycles,
+we fulfill all orders from stock.
+5% of cycles: at least one customer waits.
+NORM.S.INV() = Excel's inverse normal function.
+It converts a probability into a Z-score.
+Z-score = how many standard deviations above mean
+demand we need to stock to achieve that probability.</t>
+        </is>
+      </c>
+      <c r="E33" s="197" t="inlineStr">
+        <is>
+          <t>99% SL for A-class Turbocharger:
+NORM.S.INV(0.99) = 2.326
+→ Stock 2.33 std devs above avg demand
+→ Covers all but extreme demand spikes
+90% SL for C-class Oil Pan Gasket:
+NORM.S.INV(0.90) = 1.282
+→ Stock 1.28 std devs above avg
+→ Accept 10% chance of stockout
+   (consequence = customer waits 1-2 days
+    for a AED 380 part — acceptable)</t>
+        </is>
+      </c>
+      <c r="F33" s="198" t="inlineStr">
+        <is>
+          <t>Why NOT 99% for everything?
+Going from 99% to 99.9% SL requires
+3× MORE safety stock for the last 0.9%.
+A gasket stockout = minor delay.
+A turbocharger stockout = vehicle off road.
+Tiered SL matches SS investment to
+the ACTUAL BUSINESS IMPACT of stockout.
+This is what S&amp;OP alignment is for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  HOW TO USE THIS SHEET DURING YOUR PRESENTATION — Reference Guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="160" customHeight="1">
+      <c r="A36" s="210" t="inlineStr">
+        <is>
+          <t>PRESENTATION FLOW:
+1. START with the MONTHLY_DEMAND_DATA sheet. Point to columns F-Q. Say:
+   'These are our actual monthly demand figures for each part. From these 12 numbers, Excel calculates the standard deviation (col T) and CV (col U) automatically.'
+2. Then point to CV column U. Say:
+   'CV = Standard Deviation ÷ Mean. It tells us HOW PREDICTABLE demand is. Under 0.10 = stable. Over 0.30 = sporadic. 70% of our parts are sporadic — that's why standard SAP APO fails us.'
+3. Then point to XYZ column W. Say:
+   'The CV threshold assigns each part to X, Y, or Z class. Z-class needs a different forecasting method called SBA.'
+4. Move to ABC. Point to annual value and cumul%. Say:
+   'ABC ranks parts by annual spend. Our top 21 parts — just 42% of the portfolio — account for 69% of spend. These get maximum attention.'
+5. Combine: 'The combined class — AZ, CZ etc. — determines everything: forecasting method, safety stock formula, review frequency, and SMOB action. This is systematic inventory management, not guesswork.'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -12931,6 +20057,10 @@
           <t>Total Portfolio Value (AED)</t>
         </is>
       </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="4" t="n"/>
       <c r="F35" s="126">
         <f>SUM(F8:F32)</f>
         <v/>
@@ -12942,6 +20072,10 @@
           <t>Total Expected Recovery (AED)</t>
         </is>
       </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="4" t="n"/>
       <c r="F36" s="126">
         <f>SUM(J8:J32)</f>
         <v/>
@@ -12953,6 +20087,10 @@
           <t>Total Write-Down (AED)</t>
         </is>
       </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="4" t="n"/>
       <c r="F37" s="126">
         <f>SUM(K8:K32)</f>
         <v/>
@@ -12964,6 +20102,10 @@
           <t>Net Working Capital Released (AED)</t>
         </is>
       </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="4" t="n"/>
       <c r="F38" s="126">
         <f>F35+F36-F37</f>
         <v/>
@@ -12978,8 +20120,8 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14770,10 +21912,16 @@
           <t>Total Additional Units Required</t>
         </is>
       </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="4" t="n"/>
       <c r="F35" s="126">
         <f>SUM(F13:F32)</f>
         <v/>
       </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="4" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="61" t="inlineStr">
@@ -14781,10 +21929,16 @@
           <t>Total Bridge Stock Investment (AED)</t>
         </is>
       </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="4" t="n"/>
       <c r="F36" s="126">
         <f>SUM(G13:G32)</f>
         <v/>
       </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="4" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="61" t="inlineStr">
@@ -14792,10 +21946,16 @@
           <t>Current SS Value (AED)</t>
         </is>
       </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="4" t="n"/>
       <c r="F37" s="126">
         <f>SUM(D13:D32)*100</f>
         <v/>
       </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
